--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12360,6 +12360,324 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>114785375</v>
+      </c>
+      <c r="B109" t="n">
+        <v>90237</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kårsta_SO_Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>685317</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6616621</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>114785449</v>
+      </c>
+      <c r="B110" t="n">
+        <v>90517</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>658</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kårsta_SO_Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>685167</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6616546</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>114785372</v>
+      </c>
+      <c r="B111" t="n">
+        <v>90237</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kårsta_SO_Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>685273</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6616592</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12678,6 +12678,114 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>114830944</v>
+      </c>
+      <c r="B112" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>685227</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6616586</v>
+      </c>
+      <c r="S112" t="n">
+        <v>20</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -12786,6 +12786,109 @@
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>114856209</v>
+      </c>
+      <c r="B113" t="n">
+        <v>90240</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>685324</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6616623</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12889,6 +12889,109 @@
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>114885495</v>
+      </c>
+      <c r="B114" t="n">
+        <v>74534</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>685353</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6616602</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12992,6 +12992,112 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>115126673</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79068</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog nordost om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>685541</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6616490</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13098,6 +13098,112 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115137265</v>
+      </c>
+      <c r="B116" t="n">
+        <v>90274</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Barrnaturskog sydost om Kårsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>685442</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6616566</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13306,6 +13306,1058 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120060028</v>
+      </c>
+      <c r="B118" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>685455</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6616507</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120059783</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>685377</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6616524</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120060165</v>
+      </c>
+      <c r="B120" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>685455</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6616498</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120062340</v>
+      </c>
+      <c r="B121" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>685377</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6616544</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120061242</v>
+      </c>
+      <c r="B122" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>685386</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6616611</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120059973</v>
+      </c>
+      <c r="B123" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>685423</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6616521</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120060384</v>
+      </c>
+      <c r="B124" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>685464</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6616493</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120059941</v>
+      </c>
+      <c r="B125" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>685412</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6616537</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120061200</v>
+      </c>
+      <c r="B126" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>685378</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6616567</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120060028</v>
+        <v>120059941</v>
       </c>
       <c r="B118" t="n">
         <v>97907</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685455</v>
+        <v>685412</v>
       </c>
       <c r="R118" t="n">
-        <v>6616507</v>
+        <v>6616537</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120059783</v>
+        <v>120060165</v>
       </c>
       <c r="B119" t="n">
         <v>97907</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685377</v>
+        <v>685455</v>
       </c>
       <c r="R119" t="n">
-        <v>6616524</v>
+        <v>6616498</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13540,7 +13540,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060165</v>
+        <v>120061242</v>
       </c>
       <c r="B120" t="n">
         <v>97907</v>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13594,10 +13594,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685455</v>
+        <v>685386</v>
       </c>
       <c r="R120" t="n">
-        <v>6616498</v>
+        <v>6616611</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120062340</v>
+        <v>120059783</v>
       </c>
       <c r="B121" t="n">
         <v>97907</v>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13713,7 +13713,7 @@
         <v>685377</v>
       </c>
       <c r="R121" t="n">
-        <v>6616544</v>
+        <v>6616524</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120061242</v>
+        <v>120060384</v>
       </c>
       <c r="B122" t="n">
         <v>97907</v>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13820,16 +13820,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685386</v>
+        <v>685464</v>
       </c>
       <c r="R122" t="n">
-        <v>6616611</v>
+        <v>6616493</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13870,6 +13872,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13888,7 +13891,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120059973</v>
+        <v>120061200</v>
       </c>
       <c r="B123" t="n">
         <v>97907</v>
@@ -13923,7 +13926,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13933,7 +13936,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13942,10 +13945,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685423</v>
+        <v>685378</v>
       </c>
       <c r="R123" t="n">
-        <v>6616521</v>
+        <v>6616567</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13978,6 +13981,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14004,7 +14012,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120060384</v>
+        <v>120062340</v>
       </c>
       <c r="B124" t="n">
         <v>97907</v>
@@ -14039,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14052,18 +14060,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685464</v>
+        <v>685377</v>
       </c>
       <c r="R124" t="n">
-        <v>6616493</v>
+        <v>6616544</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14104,7 +14110,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14123,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120059941</v>
+        <v>120059973</v>
       </c>
       <c r="B125" t="n">
         <v>97907</v>
@@ -14158,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14177,10 +14182,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685412</v>
+        <v>685423</v>
       </c>
       <c r="R125" t="n">
-        <v>6616537</v>
+        <v>6616521</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14239,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120061200</v>
+        <v>120060028</v>
       </c>
       <c r="B126" t="n">
         <v>97907</v>
@@ -14274,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14284,7 +14289,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14293,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685378</v>
+        <v>685455</v>
       </c>
       <c r="R126" t="n">
-        <v>6616567</v>
+        <v>6616507</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14329,11 +14334,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120059941</v>
+        <v>120059973</v>
       </c>
       <c r="B118" t="n">
         <v>97907</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685412</v>
+        <v>685423</v>
       </c>
       <c r="R118" t="n">
-        <v>6616537</v>
+        <v>6616521</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120060165</v>
+        <v>120061200</v>
       </c>
       <c r="B119" t="n">
         <v>97907</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685455</v>
+        <v>685378</v>
       </c>
       <c r="R119" t="n">
-        <v>6616498</v>
+        <v>6616567</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13514,6 +13514,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13540,7 +13545,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120061242</v>
+        <v>120060165</v>
       </c>
       <c r="B120" t="n">
         <v>97907</v>
@@ -13575,7 +13580,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13594,10 +13599,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685386</v>
+        <v>685455</v>
       </c>
       <c r="R120" t="n">
-        <v>6616611</v>
+        <v>6616498</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13656,7 +13661,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120059783</v>
+        <v>120061242</v>
       </c>
       <c r="B121" t="n">
         <v>97907</v>
@@ -13691,7 +13696,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13701,7 +13706,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13710,10 +13715,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685377</v>
+        <v>685386</v>
       </c>
       <c r="R121" t="n">
-        <v>6616524</v>
+        <v>6616611</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13772,7 +13777,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120060384</v>
+        <v>120062340</v>
       </c>
       <c r="B122" t="n">
         <v>97907</v>
@@ -13807,7 +13812,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13820,18 +13825,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685464</v>
+        <v>685377</v>
       </c>
       <c r="R122" t="n">
-        <v>6616493</v>
+        <v>6616544</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13872,7 +13875,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13891,7 +13893,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120061200</v>
+        <v>120060028</v>
       </c>
       <c r="B123" t="n">
         <v>97907</v>
@@ -13926,7 +13928,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13936,7 +13938,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13945,10 +13947,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685378</v>
+        <v>685455</v>
       </c>
       <c r="R123" t="n">
-        <v>6616567</v>
+        <v>6616507</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13981,11 +13983,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14012,7 +14009,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120062340</v>
+        <v>120059941</v>
       </c>
       <c r="B124" t="n">
         <v>97907</v>
@@ -14047,7 +14044,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14066,10 +14063,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685377</v>
+        <v>685412</v>
       </c>
       <c r="R124" t="n">
-        <v>6616544</v>
+        <v>6616537</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14128,7 +14125,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120059973</v>
+        <v>120060384</v>
       </c>
       <c r="B125" t="n">
         <v>97907</v>
@@ -14163,7 +14160,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14176,16 +14173,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685423</v>
+        <v>685464</v>
       </c>
       <c r="R125" t="n">
-        <v>6616521</v>
+        <v>6616493</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14226,6 +14225,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120060028</v>
+        <v>120059783</v>
       </c>
       <c r="B126" t="n">
         <v>97907</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685455</v>
+        <v>685377</v>
       </c>
       <c r="R126" t="n">
-        <v>6616507</v>
+        <v>6616524</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120059973</v>
+        <v>120061242</v>
       </c>
       <c r="B118" t="n">
         <v>97907</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685423</v>
+        <v>685386</v>
       </c>
       <c r="R118" t="n">
-        <v>6616521</v>
+        <v>6616611</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120061200</v>
+        <v>120059973</v>
       </c>
       <c r="B119" t="n">
         <v>97907</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685378</v>
+        <v>685423</v>
       </c>
       <c r="R119" t="n">
-        <v>6616567</v>
+        <v>6616521</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13514,11 +13514,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13545,7 +13540,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060165</v>
+        <v>120059941</v>
       </c>
       <c r="B120" t="n">
         <v>97907</v>
@@ -13580,7 +13575,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13599,10 +13594,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685455</v>
+        <v>685412</v>
       </c>
       <c r="R120" t="n">
-        <v>6616498</v>
+        <v>6616537</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13661,7 +13656,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120061242</v>
+        <v>120061200</v>
       </c>
       <c r="B121" t="n">
         <v>97907</v>
@@ -13696,7 +13691,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13706,7 +13701,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13715,10 +13710,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685386</v>
+        <v>685378</v>
       </c>
       <c r="R121" t="n">
-        <v>6616611</v>
+        <v>6616567</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13751,6 +13746,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14009,7 +14009,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120059941</v>
+        <v>120060384</v>
       </c>
       <c r="B124" t="n">
         <v>97907</v>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14057,16 +14057,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685412</v>
+        <v>685464</v>
       </c>
       <c r="R124" t="n">
-        <v>6616537</v>
+        <v>6616493</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14107,6 +14109,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14125,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120060384</v>
+        <v>120059783</v>
       </c>
       <c r="B125" t="n">
         <v>97907</v>
@@ -14160,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14170,21 +14173,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685464</v>
+        <v>685377</v>
       </c>
       <c r="R125" t="n">
-        <v>6616493</v>
+        <v>6616524</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14225,7 +14226,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120059783</v>
+        <v>120060165</v>
       </c>
       <c r="B126" t="n">
         <v>97907</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685377</v>
+        <v>685455</v>
       </c>
       <c r="R126" t="n">
-        <v>6616524</v>
+        <v>6616498</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13311,7 +13311,7 @@
         <v>120061242</v>
       </c>
       <c r="B118" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13424,10 +13424,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120059973</v>
+        <v>120060384</v>
       </c>
       <c r="B119" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13472,16 +13472,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685423</v>
+        <v>685464</v>
       </c>
       <c r="R119" t="n">
-        <v>6616521</v>
+        <v>6616493</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13522,6 +13524,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13540,10 +13543,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120059941</v>
+        <v>120062340</v>
       </c>
       <c r="B120" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13575,7 +13578,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13594,10 +13597,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685412</v>
+        <v>685377</v>
       </c>
       <c r="R120" t="n">
-        <v>6616537</v>
+        <v>6616544</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13656,10 +13659,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120061200</v>
+        <v>120059941</v>
       </c>
       <c r="B121" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13691,7 +13694,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13701,7 +13704,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13710,10 +13713,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685378</v>
+        <v>685412</v>
       </c>
       <c r="R121" t="n">
-        <v>6616567</v>
+        <v>6616537</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13746,11 +13749,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13777,10 +13775,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120062340</v>
+        <v>120060165</v>
       </c>
       <c r="B122" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13812,7 +13810,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13831,10 +13829,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685377</v>
+        <v>685455</v>
       </c>
       <c r="R122" t="n">
-        <v>6616544</v>
+        <v>6616498</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13893,10 +13891,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120060028</v>
+        <v>120061200</v>
       </c>
       <c r="B123" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13928,7 +13926,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13938,7 +13936,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13947,10 +13945,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685455</v>
+        <v>685378</v>
       </c>
       <c r="R123" t="n">
-        <v>6616507</v>
+        <v>6616567</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,6 +13981,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14009,10 +14012,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120060384</v>
+        <v>120059973</v>
       </c>
       <c r="B124" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14044,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14057,18 +14060,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685464</v>
+        <v>685423</v>
       </c>
       <c r="R124" t="n">
-        <v>6616493</v>
+        <v>6616521</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14109,7 +14110,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>120059783</v>
       </c>
       <c r="B125" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14244,10 +14244,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120060165</v>
+        <v>120060028</v>
       </c>
       <c r="B126" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14301,7 +14301,7 @@
         <v>685455</v>
       </c>
       <c r="R126" t="n">
-        <v>6616498</v>
+        <v>6616507</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14357,6 +14357,1636 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120338810</v>
+      </c>
+      <c r="B127" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>685273</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6616552</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120339332</v>
+      </c>
+      <c r="B128" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>685320</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6616546</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>120338589</v>
+      </c>
+      <c r="B129" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>685270</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6616606</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>120339020</v>
+      </c>
+      <c r="B130" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>685309</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6616517</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>120339165</v>
+      </c>
+      <c r="B131" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>685308</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6616558</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>120338434</v>
+      </c>
+      <c r="B132" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>685232</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6616557</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>120339137</v>
+      </c>
+      <c r="B133" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>685307</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6616548</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>120339094</v>
+      </c>
+      <c r="B134" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>685308</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6616538</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>120338350</v>
+      </c>
+      <c r="B135" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>685218</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6616544</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>120338911</v>
+      </c>
+      <c r="B136" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>685292</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6616525</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>120338868</v>
+      </c>
+      <c r="B137" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>685276</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6616534</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>120338536</v>
+      </c>
+      <c r="B138" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>685260</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6616575</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>120339033</v>
+      </c>
+      <c r="B139" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>685308</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6616531</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>120338728</v>
+      </c>
+      <c r="B140" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>685284</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6616565</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120060384</v>
+        <v>120059973</v>
       </c>
       <c r="B119" t="n">
         <v>97930</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13472,18 +13472,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685464</v>
+        <v>685423</v>
       </c>
       <c r="R119" t="n">
-        <v>6616493</v>
+        <v>6616521</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13524,7 +13522,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13543,7 +13540,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120062340</v>
+        <v>120061200</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13578,7 +13575,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13588,7 +13585,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13597,10 +13594,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685377</v>
+        <v>685378</v>
       </c>
       <c r="R120" t="n">
-        <v>6616544</v>
+        <v>6616567</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13633,6 +13630,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13659,7 +13661,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120059941</v>
+        <v>120060028</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13694,7 +13696,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13713,10 +13715,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685412</v>
+        <v>685455</v>
       </c>
       <c r="R121" t="n">
-        <v>6616537</v>
+        <v>6616507</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13891,7 +13893,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120061200</v>
+        <v>120060384</v>
       </c>
       <c r="B123" t="n">
         <v>97930</v>
@@ -13926,7 +13928,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13936,19 +13938,21 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685378</v>
+        <v>685464</v>
       </c>
       <c r="R123" t="n">
-        <v>6616567</v>
+        <v>6616493</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,17 +13987,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -14012,7 +14012,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120059973</v>
+        <v>120059941</v>
       </c>
       <c r="B124" t="n">
         <v>97930</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14066,10 +14066,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685423</v>
+        <v>685412</v>
       </c>
       <c r="R124" t="n">
-        <v>6616521</v>
+        <v>6616537</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120060028</v>
+        <v>120062340</v>
       </c>
       <c r="B126" t="n">
         <v>97930</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685455</v>
+        <v>685377</v>
       </c>
       <c r="R126" t="n">
-        <v>6616507</v>
+        <v>6616544</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120338810</v>
+        <v>120338350</v>
       </c>
       <c r="B127" t="n">
         <v>97930</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14414,10 +14414,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685273</v>
+        <v>685218</v>
       </c>
       <c r="R127" t="n">
-        <v>6616552</v>
+        <v>6616544</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14476,7 +14476,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120339332</v>
+        <v>120339094</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685320</v>
+        <v>685308</v>
       </c>
       <c r="R128" t="n">
-        <v>6616546</v>
+        <v>6616538</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120338589</v>
+        <v>120338728</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -14648,10 +14648,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685270</v>
+        <v>685284</v>
       </c>
       <c r="R129" t="n">
-        <v>6616606</v>
+        <v>6616565</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14711,7 +14711,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120339020</v>
+        <v>120338810</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685309</v>
+        <v>685273</v>
       </c>
       <c r="R130" t="n">
-        <v>6616517</v>
+        <v>6616552</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14943,7 +14943,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120338434</v>
+        <v>120339332</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14997,10 +14997,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685232</v>
+        <v>685320</v>
       </c>
       <c r="R132" t="n">
-        <v>6616557</v>
+        <v>6616546</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15059,7 +15059,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120339137</v>
+        <v>120338589</v>
       </c>
       <c r="B133" t="n">
         <v>97930</v>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15107,16 +15107,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685307</v>
+        <v>685270</v>
       </c>
       <c r="R133" t="n">
-        <v>6616548</v>
+        <v>6616606</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15157,6 +15159,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15175,7 +15178,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120339094</v>
+        <v>120339137</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15210,7 +15213,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15229,10 +15232,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685308</v>
+        <v>685307</v>
       </c>
       <c r="R134" t="n">
-        <v>6616538</v>
+        <v>6616548</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15291,7 +15294,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120338350</v>
+        <v>120339020</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15326,7 +15329,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15336,7 +15339,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15345,10 +15348,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685218</v>
+        <v>685309</v>
       </c>
       <c r="R135" t="n">
-        <v>6616544</v>
+        <v>6616517</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15407,7 +15410,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120338911</v>
+        <v>120338536</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15461,10 +15464,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685292</v>
+        <v>685260</v>
       </c>
       <c r="R136" t="n">
-        <v>6616525</v>
+        <v>6616575</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15523,7 +15526,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120338868</v>
+        <v>120339033</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15558,7 +15561,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15577,10 +15580,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685276</v>
+        <v>685308</v>
       </c>
       <c r="R137" t="n">
-        <v>6616534</v>
+        <v>6616531</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,7 +15642,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120338536</v>
+        <v>120338868</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15674,7 +15677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15693,10 +15696,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685260</v>
+        <v>685276</v>
       </c>
       <c r="R138" t="n">
-        <v>6616575</v>
+        <v>6616534</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15755,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120339033</v>
+        <v>120338434</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15790,7 +15793,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15809,10 +15812,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685308</v>
+        <v>685232</v>
       </c>
       <c r="R139" t="n">
-        <v>6616531</v>
+        <v>6616557</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15871,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120338728</v>
+        <v>120338911</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15906,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15916,21 +15919,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685284</v>
+        <v>685292</v>
       </c>
       <c r="R140" t="n">
-        <v>6616565</v>
+        <v>6616525</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15971,7 +15972,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13540,7 +13540,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120061200</v>
+        <v>120060028</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13594,10 +13594,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685378</v>
+        <v>685455</v>
       </c>
       <c r="R120" t="n">
-        <v>6616567</v>
+        <v>6616507</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13630,11 +13630,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13661,7 +13656,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120060028</v>
+        <v>120060384</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13696,7 +13691,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13709,16 +13704,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685455</v>
+        <v>685464</v>
       </c>
       <c r="R121" t="n">
-        <v>6616507</v>
+        <v>6616493</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13759,6 +13756,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13777,7 +13775,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120060165</v>
+        <v>120059941</v>
       </c>
       <c r="B122" t="n">
         <v>97930</v>
@@ -13812,7 +13810,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13831,10 +13829,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685455</v>
+        <v>685412</v>
       </c>
       <c r="R122" t="n">
-        <v>6616498</v>
+        <v>6616537</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13893,7 +13891,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120060384</v>
+        <v>120061200</v>
       </c>
       <c r="B123" t="n">
         <v>97930</v>
@@ -13928,7 +13926,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13938,21 +13936,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685464</v>
+        <v>685378</v>
       </c>
       <c r="R123" t="n">
-        <v>6616493</v>
+        <v>6616567</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13987,13 +13983,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -14012,7 +14012,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120059941</v>
+        <v>120060165</v>
       </c>
       <c r="B124" t="n">
         <v>97930</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14066,10 +14066,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685412</v>
+        <v>685455</v>
       </c>
       <c r="R124" t="n">
-        <v>6616537</v>
+        <v>6616498</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120338350</v>
+        <v>120338728</v>
       </c>
       <c r="B127" t="n">
         <v>97930</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14408,16 +14408,18 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685218</v>
+        <v>685284</v>
       </c>
       <c r="R127" t="n">
-        <v>6616544</v>
+        <v>6616565</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14458,6 +14460,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14476,7 +14479,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120339094</v>
+        <v>120339165</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14511,7 +14514,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14533,7 +14536,7 @@
         <v>685308</v>
       </c>
       <c r="R128" t="n">
-        <v>6616538</v>
+        <v>6616558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14592,7 +14595,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120338728</v>
+        <v>120338434</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14627,7 +14630,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14637,21 +14640,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685284</v>
+        <v>685232</v>
       </c>
       <c r="R129" t="n">
-        <v>6616565</v>
+        <v>6616557</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14692,7 +14693,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14711,7 +14711,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120338810</v>
+        <v>120339246</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685273</v>
+        <v>685320</v>
       </c>
       <c r="R130" t="n">
-        <v>6616552</v>
+        <v>6616546</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14827,7 +14827,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120339165</v>
+        <v>120339094</v>
       </c>
       <c r="B131" t="n">
         <v>97930</v>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14884,7 +14884,7 @@
         <v>685308</v>
       </c>
       <c r="R131" t="n">
-        <v>6616558</v>
+        <v>6616538</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14943,7 +14943,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120339332</v>
+        <v>120338868</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14997,10 +14997,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685320</v>
+        <v>685276</v>
       </c>
       <c r="R132" t="n">
-        <v>6616546</v>
+        <v>6616534</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15178,7 +15178,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120339137</v>
+        <v>120338810</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15232,10 +15232,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685307</v>
+        <v>685273</v>
       </c>
       <c r="R134" t="n">
-        <v>6616548</v>
+        <v>6616552</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120339020</v>
+        <v>120339137</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15348,10 +15348,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685309</v>
+        <v>685307</v>
       </c>
       <c r="R135" t="n">
-        <v>6616517</v>
+        <v>6616548</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120338536</v>
+        <v>120338350</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15464,10 +15464,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685260</v>
+        <v>685218</v>
       </c>
       <c r="R136" t="n">
-        <v>6616575</v>
+        <v>6616544</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120339033</v>
+        <v>120338536</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685308</v>
+        <v>685260</v>
       </c>
       <c r="R137" t="n">
-        <v>6616531</v>
+        <v>6616575</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15642,7 +15642,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120338868</v>
+        <v>120338911</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685276</v>
+        <v>685292</v>
       </c>
       <c r="R138" t="n">
-        <v>6616534</v>
+        <v>6616525</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120338434</v>
+        <v>120339033</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685232</v>
+        <v>685308</v>
       </c>
       <c r="R139" t="n">
-        <v>6616557</v>
+        <v>6616531</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15874,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120338911</v>
+        <v>120339020</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685292</v>
+        <v>685309</v>
       </c>
       <c r="R140" t="n">
-        <v>6616525</v>
+        <v>6616517</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120061242</v>
+        <v>120060028</v>
       </c>
       <c r="B118" t="n">
         <v>97930</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685386</v>
+        <v>685455</v>
       </c>
       <c r="R118" t="n">
-        <v>6616611</v>
+        <v>6616507</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120059973</v>
+        <v>120061200</v>
       </c>
       <c r="B119" t="n">
         <v>97930</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685423</v>
+        <v>685378</v>
       </c>
       <c r="R119" t="n">
-        <v>6616521</v>
+        <v>6616567</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13514,6 +13514,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13540,7 +13545,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060028</v>
+        <v>120060165</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13575,7 +13580,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13597,7 +13602,7 @@
         <v>685455</v>
       </c>
       <c r="R120" t="n">
-        <v>6616507</v>
+        <v>6616498</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13656,7 +13661,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120060384</v>
+        <v>120059783</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13691,7 +13696,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13701,21 +13706,19 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685464</v>
+        <v>685377</v>
       </c>
       <c r="R121" t="n">
-        <v>6616493</v>
+        <v>6616524</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13756,7 +13759,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13775,7 +13777,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120059941</v>
+        <v>120061242</v>
       </c>
       <c r="B122" t="n">
         <v>97930</v>
@@ -13810,7 +13812,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13829,10 +13831,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685412</v>
+        <v>685386</v>
       </c>
       <c r="R122" t="n">
-        <v>6616537</v>
+        <v>6616611</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13891,7 +13893,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120061200</v>
+        <v>120059973</v>
       </c>
       <c r="B123" t="n">
         <v>97930</v>
@@ -13926,7 +13928,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13936,7 +13938,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13945,10 +13947,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685378</v>
+        <v>685423</v>
       </c>
       <c r="R123" t="n">
-        <v>6616567</v>
+        <v>6616521</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13981,11 +13983,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14012,7 +14009,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120060165</v>
+        <v>120060384</v>
       </c>
       <c r="B124" t="n">
         <v>97930</v>
@@ -14047,7 +14044,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14060,16 +14057,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685455</v>
+        <v>685464</v>
       </c>
       <c r="R124" t="n">
-        <v>6616498</v>
+        <v>6616493</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14110,6 +14109,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14128,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120059783</v>
+        <v>120062340</v>
       </c>
       <c r="B125" t="n">
         <v>97930</v>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14185,7 +14185,7 @@
         <v>685377</v>
       </c>
       <c r="R125" t="n">
-        <v>6616524</v>
+        <v>6616544</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120062340</v>
+        <v>120059941</v>
       </c>
       <c r="B126" t="n">
         <v>97930</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685377</v>
+        <v>685412</v>
       </c>
       <c r="R126" t="n">
-        <v>6616544</v>
+        <v>6616537</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120338728</v>
+        <v>120339033</v>
       </c>
       <c r="B127" t="n">
         <v>97930</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14405,21 +14405,19 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685284</v>
+        <v>685308</v>
       </c>
       <c r="R127" t="n">
-        <v>6616565</v>
+        <v>6616531</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14460,7 +14458,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14479,7 +14476,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120339165</v>
+        <v>120339020</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14514,7 +14511,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14533,10 +14530,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685308</v>
+        <v>685309</v>
       </c>
       <c r="R128" t="n">
-        <v>6616558</v>
+        <v>6616517</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14595,7 +14592,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120338434</v>
+        <v>120338911</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14630,7 +14627,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14649,10 +14646,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685232</v>
+        <v>685292</v>
       </c>
       <c r="R129" t="n">
-        <v>6616557</v>
+        <v>6616525</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14711,7 +14708,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120339246</v>
+        <v>120338868</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14746,7 +14743,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14765,10 +14762,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685320</v>
+        <v>685276</v>
       </c>
       <c r="R130" t="n">
-        <v>6616546</v>
+        <v>6616534</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14827,7 +14824,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120339094</v>
+        <v>120338434</v>
       </c>
       <c r="B131" t="n">
         <v>97930</v>
@@ -14862,7 +14859,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14881,10 +14878,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685308</v>
+        <v>685232</v>
       </c>
       <c r="R131" t="n">
-        <v>6616538</v>
+        <v>6616557</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14943,7 +14940,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120338868</v>
+        <v>120339246</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14978,7 +14975,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14997,10 +14994,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685276</v>
+        <v>685320</v>
       </c>
       <c r="R132" t="n">
-        <v>6616534</v>
+        <v>6616546</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15059,7 +15056,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120338589</v>
+        <v>120338536</v>
       </c>
       <c r="B133" t="n">
         <v>97930</v>
@@ -15094,7 +15091,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15107,18 +15104,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685270</v>
+        <v>685260</v>
       </c>
       <c r="R133" t="n">
-        <v>6616606</v>
+        <v>6616575</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15159,7 +15154,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15178,7 +15172,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120338810</v>
+        <v>120338350</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15213,7 +15207,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15223,7 +15217,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15232,10 +15226,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685273</v>
+        <v>685218</v>
       </c>
       <c r="R134" t="n">
-        <v>6616552</v>
+        <v>6616544</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15294,7 +15288,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120339137</v>
+        <v>120338589</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15329,7 +15323,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15342,16 +15336,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685307</v>
+        <v>685270</v>
       </c>
       <c r="R135" t="n">
-        <v>6616548</v>
+        <v>6616606</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15392,6 +15388,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15410,7 +15407,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120338350</v>
+        <v>120339165</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15445,7 +15442,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15455,7 +15452,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15464,10 +15461,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685218</v>
+        <v>685308</v>
       </c>
       <c r="R136" t="n">
-        <v>6616544</v>
+        <v>6616558</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15526,7 +15523,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120338536</v>
+        <v>120338728</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15561,7 +15558,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15571,19 +15568,21 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685260</v>
+        <v>685284</v>
       </c>
       <c r="R137" t="n">
-        <v>6616575</v>
+        <v>6616565</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15624,6 +15623,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15642,7 +15642,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120338911</v>
+        <v>120338810</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685292</v>
+        <v>685273</v>
       </c>
       <c r="R138" t="n">
-        <v>6616525</v>
+        <v>6616552</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120339033</v>
+        <v>120339137</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685308</v>
+        <v>685307</v>
       </c>
       <c r="R139" t="n">
-        <v>6616531</v>
+        <v>6616548</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15874,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120339020</v>
+        <v>120339094</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685309</v>
+        <v>685308</v>
       </c>
       <c r="R140" t="n">
-        <v>6616517</v>
+        <v>6616538</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120060028</v>
+        <v>120061200</v>
       </c>
       <c r="B118" t="n">
         <v>97930</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685455</v>
+        <v>685378</v>
       </c>
       <c r="R118" t="n">
-        <v>6616507</v>
+        <v>6616567</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13398,6 +13398,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13424,7 +13429,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120061200</v>
+        <v>120062340</v>
       </c>
       <c r="B119" t="n">
         <v>97930</v>
@@ -13459,7 +13464,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13469,7 +13474,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13478,10 +13483,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685378</v>
+        <v>685377</v>
       </c>
       <c r="R119" t="n">
-        <v>6616567</v>
+        <v>6616544</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13514,11 +13519,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13545,7 +13545,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060165</v>
+        <v>120060384</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13593,16 +13593,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685455</v>
+        <v>685464</v>
       </c>
       <c r="R120" t="n">
-        <v>6616498</v>
+        <v>6616493</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13643,6 +13645,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13777,7 +13780,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120061242</v>
+        <v>120059941</v>
       </c>
       <c r="B122" t="n">
         <v>97930</v>
@@ -13812,7 +13815,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13831,10 +13834,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685386</v>
+        <v>685412</v>
       </c>
       <c r="R122" t="n">
-        <v>6616611</v>
+        <v>6616537</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14009,7 +14012,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120060384</v>
+        <v>120060028</v>
       </c>
       <c r="B124" t="n">
         <v>97930</v>
@@ -14044,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14057,18 +14060,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685464</v>
+        <v>685455</v>
       </c>
       <c r="R124" t="n">
-        <v>6616493</v>
+        <v>6616507</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14109,7 +14110,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14128,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120062340</v>
+        <v>120061242</v>
       </c>
       <c r="B125" t="n">
         <v>97930</v>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685377</v>
+        <v>685386</v>
       </c>
       <c r="R125" t="n">
-        <v>6616544</v>
+        <v>6616611</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120059941</v>
+        <v>120060165</v>
       </c>
       <c r="B126" t="n">
         <v>97930</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685412</v>
+        <v>685455</v>
       </c>
       <c r="R126" t="n">
-        <v>6616537</v>
+        <v>6616498</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120339033</v>
+        <v>120339165</v>
       </c>
       <c r="B127" t="n">
         <v>97930</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14417,7 +14417,7 @@
         <v>685308</v>
       </c>
       <c r="R127" t="n">
-        <v>6616531</v>
+        <v>6616558</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14476,7 +14476,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120339020</v>
+        <v>120338350</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685309</v>
+        <v>685218</v>
       </c>
       <c r="R128" t="n">
-        <v>6616517</v>
+        <v>6616544</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120338911</v>
+        <v>120339246</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14646,10 +14646,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685292</v>
+        <v>685320</v>
       </c>
       <c r="R129" t="n">
-        <v>6616525</v>
+        <v>6616546</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14708,7 +14708,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120338868</v>
+        <v>120338434</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14762,10 +14762,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685276</v>
+        <v>685232</v>
       </c>
       <c r="R130" t="n">
-        <v>6616534</v>
+        <v>6616557</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14824,7 +14824,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120338434</v>
+        <v>120339137</v>
       </c>
       <c r="B131" t="n">
         <v>97930</v>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14878,10 +14878,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685232</v>
+        <v>685307</v>
       </c>
       <c r="R131" t="n">
-        <v>6616557</v>
+        <v>6616548</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14940,7 +14940,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120339246</v>
+        <v>120338728</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14985,19 +14985,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685320</v>
+        <v>685284</v>
       </c>
       <c r="R132" t="n">
-        <v>6616546</v>
+        <v>6616565</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15038,6 +15040,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15172,7 +15175,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120338350</v>
+        <v>120339033</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15217,7 +15220,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15226,10 +15229,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685218</v>
+        <v>685308</v>
       </c>
       <c r="R134" t="n">
-        <v>6616544</v>
+        <v>6616531</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15288,7 +15291,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120338589</v>
+        <v>120339094</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15323,7 +15326,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15336,18 +15339,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685270</v>
+        <v>685308</v>
       </c>
       <c r="R135" t="n">
-        <v>6616606</v>
+        <v>6616538</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15388,7 +15389,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120339165</v>
+        <v>120338911</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15461,10 +15461,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685308</v>
+        <v>685292</v>
       </c>
       <c r="R136" t="n">
-        <v>6616558</v>
+        <v>6616525</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15523,7 +15523,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120338728</v>
+        <v>120338810</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15568,21 +15568,19 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685284</v>
+        <v>685273</v>
       </c>
       <c r="R137" t="n">
-        <v>6616565</v>
+        <v>6616552</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15623,7 +15621,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15642,7 +15639,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120338810</v>
+        <v>120339020</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15677,7 +15674,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15696,10 +15693,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685273</v>
+        <v>685309</v>
       </c>
       <c r="R138" t="n">
-        <v>6616552</v>
+        <v>6616517</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,7 +15755,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120339137</v>
+        <v>120338589</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15793,7 +15790,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15806,16 +15803,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685307</v>
+        <v>685270</v>
       </c>
       <c r="R139" t="n">
-        <v>6616548</v>
+        <v>6616606</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15856,6 +15855,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15874,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120339094</v>
+        <v>120338868</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685308</v>
+        <v>685276</v>
       </c>
       <c r="R140" t="n">
-        <v>6616538</v>
+        <v>6616534</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -15059,7 +15059,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120338536</v>
+        <v>120339033</v>
       </c>
       <c r="B133" t="n">
         <v>97930</v>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15113,10 +15113,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685260</v>
+        <v>685308</v>
       </c>
       <c r="R133" t="n">
-        <v>6616575</v>
+        <v>6616531</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15175,7 +15175,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120339033</v>
+        <v>120338536</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685308</v>
+        <v>685260</v>
       </c>
       <c r="R134" t="n">
-        <v>6616531</v>
+        <v>6616575</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120061200</v>
+        <v>120059973</v>
       </c>
       <c r="B118" t="n">
         <v>97930</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685378</v>
+        <v>685423</v>
       </c>
       <c r="R118" t="n">
-        <v>6616567</v>
+        <v>6616521</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13398,11 +13398,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13545,7 +13540,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060384</v>
+        <v>120060165</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13580,7 +13575,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13593,18 +13588,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685464</v>
+        <v>685455</v>
       </c>
       <c r="R120" t="n">
-        <v>6616493</v>
+        <v>6616498</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13645,7 +13638,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13664,7 +13656,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120059783</v>
+        <v>120060384</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13699,7 +13691,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13709,19 +13701,21 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685377</v>
+        <v>685464</v>
       </c>
       <c r="R121" t="n">
-        <v>6616524</v>
+        <v>6616493</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13762,6 +13756,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13780,7 +13775,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120059941</v>
+        <v>120061200</v>
       </c>
       <c r="B122" t="n">
         <v>97930</v>
@@ -13815,7 +13810,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13825,7 +13820,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13834,10 +13829,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685412</v>
+        <v>685378</v>
       </c>
       <c r="R122" t="n">
-        <v>6616537</v>
+        <v>6616567</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13870,6 +13865,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13896,7 +13896,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120059973</v>
+        <v>120061242</v>
       </c>
       <c r="B123" t="n">
         <v>97930</v>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13950,10 +13950,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685423</v>
+        <v>685386</v>
       </c>
       <c r="R123" t="n">
-        <v>6616521</v>
+        <v>6616611</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14128,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120061242</v>
+        <v>120059941</v>
       </c>
       <c r="B125" t="n">
         <v>97930</v>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685386</v>
+        <v>685412</v>
       </c>
       <c r="R125" t="n">
-        <v>6616611</v>
+        <v>6616537</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120060165</v>
+        <v>120059783</v>
       </c>
       <c r="B126" t="n">
         <v>97930</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685455</v>
+        <v>685377</v>
       </c>
       <c r="R126" t="n">
-        <v>6616498</v>
+        <v>6616524</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14476,7 +14476,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120338350</v>
+        <v>120339246</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685218</v>
+        <v>685320</v>
       </c>
       <c r="R128" t="n">
-        <v>6616544</v>
+        <v>6616546</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120339246</v>
+        <v>120339020</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14646,10 +14646,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685320</v>
+        <v>685309</v>
       </c>
       <c r="R129" t="n">
-        <v>6616546</v>
+        <v>6616517</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14708,7 +14708,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120338434</v>
+        <v>120339033</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14762,10 +14762,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685232</v>
+        <v>685308</v>
       </c>
       <c r="R130" t="n">
-        <v>6616557</v>
+        <v>6616531</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14824,7 +14824,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120339137</v>
+        <v>120338589</v>
       </c>
       <c r="B131" t="n">
         <v>97930</v>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14872,16 +14872,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685307</v>
+        <v>685270</v>
       </c>
       <c r="R131" t="n">
-        <v>6616548</v>
+        <v>6616606</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14922,6 +14924,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14940,7 +14943,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120338728</v>
+        <v>120338911</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14975,7 +14978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14985,21 +14988,19 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685284</v>
+        <v>685292</v>
       </c>
       <c r="R132" t="n">
-        <v>6616565</v>
+        <v>6616525</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15040,7 +15041,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15059,7 +15059,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120339033</v>
+        <v>120338728</v>
       </c>
       <c r="B133" t="n">
         <v>97930</v>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15104,19 +15104,21 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685308</v>
+        <v>685284</v>
       </c>
       <c r="R133" t="n">
-        <v>6616531</v>
+        <v>6616565</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15157,6 +15159,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15175,7 +15178,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120338536</v>
+        <v>120339137</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15210,7 +15213,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15229,10 +15232,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685260</v>
+        <v>685307</v>
       </c>
       <c r="R134" t="n">
-        <v>6616575</v>
+        <v>6616548</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15407,7 +15410,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120338911</v>
+        <v>120338868</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15442,7 +15445,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15461,10 +15464,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685292</v>
+        <v>685276</v>
       </c>
       <c r="R136" t="n">
-        <v>6616525</v>
+        <v>6616534</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15523,7 +15526,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120338810</v>
+        <v>120338434</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15558,7 +15561,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15577,10 +15580,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685273</v>
+        <v>685232</v>
       </c>
       <c r="R137" t="n">
-        <v>6616552</v>
+        <v>6616557</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,7 +15642,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120339020</v>
+        <v>120338810</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15674,7 +15677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15693,10 +15696,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685309</v>
+        <v>685273</v>
       </c>
       <c r="R138" t="n">
-        <v>6616517</v>
+        <v>6616552</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15755,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120338589</v>
+        <v>120338536</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15790,7 +15793,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15803,18 +15806,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685270</v>
+        <v>685260</v>
       </c>
       <c r="R139" t="n">
-        <v>6616606</v>
+        <v>6616575</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15855,7 +15856,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15874,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120338868</v>
+        <v>120338350</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685276</v>
+        <v>685218</v>
       </c>
       <c r="R140" t="n">
-        <v>6616534</v>
+        <v>6616544</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -13308,7 +13308,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120059973</v>
+        <v>120060165</v>
       </c>
       <c r="B118" t="n">
         <v>97930</v>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13362,10 +13362,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685423</v>
+        <v>685455</v>
       </c>
       <c r="R118" t="n">
-        <v>6616521</v>
+        <v>6616498</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13424,7 +13424,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120062340</v>
+        <v>120060384</v>
       </c>
       <c r="B119" t="n">
         <v>97930</v>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13472,16 +13472,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685377</v>
+        <v>685464</v>
       </c>
       <c r="R119" t="n">
-        <v>6616544</v>
+        <v>6616493</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13522,6 +13524,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13540,7 +13543,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120060165</v>
+        <v>120059941</v>
       </c>
       <c r="B120" t="n">
         <v>97930</v>
@@ -13575,7 +13578,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13594,10 +13597,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685455</v>
+        <v>685412</v>
       </c>
       <c r="R120" t="n">
-        <v>6616498</v>
+        <v>6616537</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13656,7 +13659,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120060384</v>
+        <v>120060028</v>
       </c>
       <c r="B121" t="n">
         <v>97930</v>
@@ -13691,7 +13694,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13704,18 +13707,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685464</v>
+        <v>685455</v>
       </c>
       <c r="R121" t="n">
-        <v>6616493</v>
+        <v>6616507</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13756,7 +13757,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13775,7 +13775,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120061200</v>
+        <v>120059973</v>
       </c>
       <c r="B122" t="n">
         <v>97930</v>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13829,10 +13829,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685378</v>
+        <v>685423</v>
       </c>
       <c r="R122" t="n">
-        <v>6616567</v>
+        <v>6616521</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13865,11 +13865,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13896,7 +13891,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120061242</v>
+        <v>120061200</v>
       </c>
       <c r="B123" t="n">
         <v>97930</v>
@@ -13931,7 +13926,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13941,7 +13936,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13950,10 +13945,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685386</v>
+        <v>685378</v>
       </c>
       <c r="R123" t="n">
-        <v>6616611</v>
+        <v>6616567</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13986,6 +13981,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14012,7 +14012,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120060028</v>
+        <v>120061242</v>
       </c>
       <c r="B124" t="n">
         <v>97930</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -14066,10 +14066,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685455</v>
+        <v>685386</v>
       </c>
       <c r="R124" t="n">
-        <v>6616507</v>
+        <v>6616611</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14128,7 +14128,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120059941</v>
+        <v>120062340</v>
       </c>
       <c r="B125" t="n">
         <v>97930</v>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685412</v>
+        <v>685377</v>
       </c>
       <c r="R125" t="n">
-        <v>6616537</v>
+        <v>6616544</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120339165</v>
+        <v>120338536</v>
       </c>
       <c r="B127" t="n">
         <v>97930</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14414,10 +14414,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685308</v>
+        <v>685260</v>
       </c>
       <c r="R127" t="n">
-        <v>6616558</v>
+        <v>6616575</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14476,7 +14476,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120339246</v>
+        <v>120338911</v>
       </c>
       <c r="B128" t="n">
         <v>97930</v>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14530,10 +14530,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685320</v>
+        <v>685292</v>
       </c>
       <c r="R128" t="n">
-        <v>6616546</v>
+        <v>6616525</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120339020</v>
+        <v>120338434</v>
       </c>
       <c r="B129" t="n">
         <v>97930</v>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14646,10 +14646,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685309</v>
+        <v>685232</v>
       </c>
       <c r="R129" t="n">
-        <v>6616517</v>
+        <v>6616557</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14708,7 +14708,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120339033</v>
+        <v>120339332</v>
       </c>
       <c r="B130" t="n">
         <v>97930</v>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14762,10 +14762,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685308</v>
+        <v>685320</v>
       </c>
       <c r="R130" t="n">
-        <v>6616531</v>
+        <v>6616546</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14943,7 +14943,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120338911</v>
+        <v>120338728</v>
       </c>
       <c r="B132" t="n">
         <v>97930</v>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14988,19 +14988,21 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685292</v>
+        <v>685284</v>
       </c>
       <c r="R132" t="n">
-        <v>6616525</v>
+        <v>6616565</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15041,6 +15043,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15059,7 +15062,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120338728</v>
+        <v>120339137</v>
       </c>
       <c r="B133" t="n">
         <v>97930</v>
@@ -15094,7 +15097,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15104,21 +15107,19 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685284</v>
+        <v>685307</v>
       </c>
       <c r="R133" t="n">
-        <v>6616565</v>
+        <v>6616548</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15159,7 +15160,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15178,7 +15178,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120339137</v>
+        <v>120338810</v>
       </c>
       <c r="B134" t="n">
         <v>97930</v>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15232,10 +15232,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685307</v>
+        <v>685273</v>
       </c>
       <c r="R134" t="n">
-        <v>6616548</v>
+        <v>6616552</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120339094</v>
+        <v>120339033</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15351,7 +15351,7 @@
         <v>685308</v>
       </c>
       <c r="R135" t="n">
-        <v>6616538</v>
+        <v>6616531</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120338868</v>
+        <v>120338350</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15464,10 +15464,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685276</v>
+        <v>685218</v>
       </c>
       <c r="R136" t="n">
-        <v>6616534</v>
+        <v>6616544</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120338434</v>
+        <v>120339094</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685232</v>
+        <v>685308</v>
       </c>
       <c r="R137" t="n">
-        <v>6616557</v>
+        <v>6616538</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15642,7 +15642,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120338810</v>
+        <v>120338868</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685273</v>
+        <v>685276</v>
       </c>
       <c r="R138" t="n">
-        <v>6616552</v>
+        <v>6616534</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120338536</v>
+        <v>120339020</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685260</v>
+        <v>685309</v>
       </c>
       <c r="R139" t="n">
-        <v>6616575</v>
+        <v>6616517</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15874,7 +15874,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120338350</v>
+        <v>120339165</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685218</v>
+        <v>685308</v>
       </c>
       <c r="R140" t="n">
-        <v>6616544</v>
+        <v>6616558</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY155"/>
+  <dimension ref="A1:AY157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17726,6 +17726,237 @@
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>121542947</v>
+      </c>
+      <c r="B156" t="n">
+        <v>98099</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>685522</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6616576</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Enbart vinterståndare räknade pga snö. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna.</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>121543023</v>
+      </c>
+      <c r="B157" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>685481</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6616602</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17731,7 +17731,7 @@
         <v>121542947</v>
       </c>
       <c r="B156" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17728,10 +17728,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121542947</v>
+        <v>121543023</v>
       </c>
       <c r="B156" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17740,54 +17740,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>685522</v>
+        <v>685481</v>
       </c>
       <c r="R156" t="n">
-        <v>6616576</v>
+        <v>6616602</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17822,18 +17811,12 @@
           <t>2024-12-10</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Enbart vinterståndare räknade pga snö. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17852,10 +17835,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121543023</v>
+        <v>121542947</v>
       </c>
       <c r="B157" t="n">
-        <v>57371</v>
+        <v>98105</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17864,43 +17847,54 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>685481</v>
+        <v>685522</v>
       </c>
       <c r="R157" t="n">
-        <v>6616602</v>
+        <v>6616576</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17935,12 +17929,18 @@
           <t>2024-12-10</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Enbart vinterståndare räknade pga snö. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17728,10 +17728,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121543023</v>
+        <v>121542947</v>
       </c>
       <c r="B156" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17740,43 +17740,54 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>685481</v>
+        <v>685522</v>
       </c>
       <c r="R156" t="n">
-        <v>6616602</v>
+        <v>6616576</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17811,12 +17822,18 @@
           <t>2024-12-10</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Enbart vinterståndare räknade pga snö. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17835,10 +17852,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121542947</v>
+        <v>121543023</v>
       </c>
       <c r="B157" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17847,54 +17864,43 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>685522</v>
+        <v>685481</v>
       </c>
       <c r="R157" t="n">
-        <v>6616576</v>
+        <v>6616602</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17929,18 +17935,12 @@
           <t>2024-12-10</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Enbart vinterståndare räknade pga snö. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY157"/>
+  <dimension ref="A1:AY158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17957,6 +17957,108 @@
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>121649980</v>
+      </c>
+      <c r="B158" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>685534</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6616549</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17731,7 +17731,7 @@
         <v>121542947</v>
       </c>
       <c r="B156" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>121543023</v>
       </c>
       <c r="B157" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>121649980</v>
       </c>
       <c r="B158" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733242</v>
+        <v>121733164</v>
       </c>
       <c r="B158" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17956,39 +17956,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685203</v>
+        <v>685265</v>
       </c>
       <c r="R158" t="n">
-        <v>6616619</v>
+        <v>6616630</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18047,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733137</v>
+        <v>121733238</v>
       </c>
       <c r="B159" t="n">
-        <v>90728</v>
+        <v>94885</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18059,38 +18054,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685270</v>
+        <v>685200</v>
       </c>
       <c r="R159" t="n">
-        <v>6616635</v>
+        <v>6616618</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18149,10 +18144,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733202</v>
+        <v>121733137</v>
       </c>
       <c r="B160" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18165,39 +18160,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685225</v>
+        <v>685270</v>
       </c>
       <c r="R160" t="n">
-        <v>6616633</v>
+        <v>6616635</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18256,10 +18246,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733724</v>
+        <v>121733202</v>
       </c>
       <c r="B161" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18268,52 +18258,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685253</v>
+        <v>685225</v>
       </c>
       <c r="R161" t="n">
-        <v>6616553</v>
+        <v>6616633</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18372,10 +18353,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733603</v>
+        <v>121733242</v>
       </c>
       <c r="B162" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18384,40 +18365,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18426,10 +18398,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685252</v>
+        <v>685203</v>
       </c>
       <c r="R162" t="n">
-        <v>6616565</v>
+        <v>6616619</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18488,10 +18460,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733585</v>
+        <v>121733533</v>
       </c>
       <c r="B163" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18500,31 +18472,31 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18533,10 +18505,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685248</v>
+        <v>685207</v>
       </c>
       <c r="R163" t="n">
-        <v>6616566</v>
+        <v>6616580</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18595,10 +18567,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733164</v>
+        <v>121733585</v>
       </c>
       <c r="B164" t="n">
-        <v>90728</v>
+        <v>8436</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18607,38 +18579,43 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685265</v>
+        <v>685248</v>
       </c>
       <c r="R164" t="n">
-        <v>6616630</v>
+        <v>6616566</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18697,10 +18674,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733466</v>
+        <v>121733778</v>
       </c>
       <c r="B165" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18709,20 +18686,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -18733,19 +18710,19 @@
       <c r="I165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685224</v>
+        <v>685216</v>
       </c>
       <c r="R165" t="n">
-        <v>6616585</v>
+        <v>6616536</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18804,10 +18781,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733409</v>
+        <v>121733744</v>
       </c>
       <c r="B166" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18816,52 +18793,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685237</v>
+        <v>685241</v>
       </c>
       <c r="R166" t="n">
-        <v>6616591</v>
+        <v>6616545</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18920,7 +18883,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733712</v>
+        <v>121733603</v>
       </c>
       <c r="B167" t="n">
         <v>98113</v>
@@ -18955,7 +18918,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18970,14 +18933,14 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685256</v>
+        <v>685252</v>
       </c>
       <c r="R167" t="n">
-        <v>6616548</v>
+        <v>6616565</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19036,10 +18999,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733744</v>
+        <v>121733409</v>
       </c>
       <c r="B168" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19048,38 +19011,52 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685241</v>
+        <v>685237</v>
       </c>
       <c r="R168" t="n">
-        <v>6616545</v>
+        <v>6616591</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19138,10 +19115,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733238</v>
+        <v>121733724</v>
       </c>
       <c r="B169" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19150,38 +19127,52 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685200</v>
+        <v>685253</v>
       </c>
       <c r="R169" t="n">
-        <v>6616618</v>
+        <v>6616553</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19240,10 +19231,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733778</v>
+        <v>121733466</v>
       </c>
       <c r="B170" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19252,20 +19243,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19276,19 +19267,19 @@
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685216</v>
+        <v>685224</v>
       </c>
       <c r="R170" t="n">
-        <v>6616536</v>
+        <v>6616585</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19463,10 +19454,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733533</v>
+        <v>121733712</v>
       </c>
       <c r="B172" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19475,43 +19466,52 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685207</v>
+        <v>685256</v>
       </c>
       <c r="R172" t="n">
-        <v>6616580</v>
+        <v>6616548</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19942,7 +19942,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121763551</v>
+        <v>121763251</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19996,10 +19996,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685221</v>
+        <v>685224</v>
       </c>
       <c r="R176" t="n">
-        <v>6616544</v>
+        <v>6616549</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20032,11 +20032,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20063,7 +20058,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762699</v>
+        <v>121763551</v>
       </c>
       <c r="B177" t="n">
         <v>98113</v>
@@ -20098,7 +20093,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20117,10 +20112,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685226</v>
+        <v>685221</v>
       </c>
       <c r="R177" t="n">
-        <v>6616562</v>
+        <v>6616544</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20153,6 +20148,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20179,10 +20179,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121763251</v>
+        <v>121762474</v>
       </c>
       <c r="B178" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20191,52 +20191,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685224</v>
+        <v>685237</v>
       </c>
       <c r="R178" t="n">
-        <v>6616549</v>
+        <v>6616643</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20295,10 +20281,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121762474</v>
+        <v>121762699</v>
       </c>
       <c r="B179" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20307,38 +20293,52 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685237</v>
+        <v>685226</v>
       </c>
       <c r="R179" t="n">
-        <v>6616643</v>
+        <v>6616562</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AY180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20395,6 +20395,108 @@
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>121813185</v>
+      </c>
+      <c r="B180" t="n">
+        <v>90693</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>685197</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6616552</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733164</v>
+        <v>121733778</v>
       </c>
       <c r="B158" t="n">
-        <v>90728</v>
+        <v>5193</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,38 +17952,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685265</v>
+        <v>685216</v>
       </c>
       <c r="R158" t="n">
-        <v>6616630</v>
+        <v>6616536</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18047,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733238</v>
+        <v>121733724</v>
       </c>
       <c r="B159" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18054,38 +18059,52 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685200</v>
+        <v>685253</v>
       </c>
       <c r="R159" t="n">
-        <v>6616618</v>
+        <v>6616553</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18144,10 +18163,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733137</v>
+        <v>121733202</v>
       </c>
       <c r="B160" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18160,34 +18179,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685270</v>
+        <v>685225</v>
       </c>
       <c r="R160" t="n">
-        <v>6616635</v>
+        <v>6616633</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18246,10 +18270,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733202</v>
+        <v>121733603</v>
       </c>
       <c r="B161" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18258,31 +18282,40 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18291,10 +18324,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685225</v>
+        <v>685252</v>
       </c>
       <c r="R161" t="n">
-        <v>6616633</v>
+        <v>6616565</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18353,10 +18386,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733242</v>
+        <v>121733612</v>
       </c>
       <c r="B162" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18365,31 +18398,40 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18398,10 +18440,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685203</v>
+        <v>685252</v>
       </c>
       <c r="R162" t="n">
-        <v>6616619</v>
+        <v>6616565</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18460,10 +18502,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733533</v>
+        <v>121733409</v>
       </c>
       <c r="B163" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18472,31 +18514,40 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18505,10 +18556,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685207</v>
+        <v>685237</v>
       </c>
       <c r="R163" t="n">
-        <v>6616580</v>
+        <v>6616591</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18567,10 +18618,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733585</v>
+        <v>121733533</v>
       </c>
       <c r="B164" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18579,31 +18630,31 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18612,10 +18663,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685248</v>
+        <v>685207</v>
       </c>
       <c r="R164" t="n">
-        <v>6616566</v>
+        <v>6616580</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18674,10 +18725,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733778</v>
+        <v>121733164</v>
       </c>
       <c r="B165" t="n">
-        <v>5193</v>
+        <v>90728</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18686,43 +18737,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685216</v>
+        <v>685265</v>
       </c>
       <c r="R165" t="n">
-        <v>6616536</v>
+        <v>6616630</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18883,10 +18929,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733603</v>
+        <v>121733137</v>
       </c>
       <c r="B167" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18895,52 +18941,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685252</v>
+        <v>685270</v>
       </c>
       <c r="R167" t="n">
-        <v>6616565</v>
+        <v>6616635</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18999,10 +19031,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733409</v>
+        <v>121733466</v>
       </c>
       <c r="B168" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19011,40 +19043,31 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19053,10 +19076,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R168" t="n">
-        <v>6616591</v>
+        <v>6616585</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19115,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733724</v>
+        <v>121733238</v>
       </c>
       <c r="B169" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19127,52 +19150,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685253</v>
+        <v>685200</v>
       </c>
       <c r="R169" t="n">
-        <v>6616553</v>
+        <v>6616618</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19231,7 +19240,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733466</v>
+        <v>121733242</v>
       </c>
       <c r="B170" t="n">
         <v>57373</v>
@@ -19276,10 +19285,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685224</v>
+        <v>685203</v>
       </c>
       <c r="R170" t="n">
-        <v>6616585</v>
+        <v>6616619</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19338,10 +19347,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733612</v>
+        <v>121733712</v>
       </c>
       <c r="B171" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19350,52 +19359,52 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685252</v>
+        <v>685256</v>
       </c>
       <c r="R171" t="n">
-        <v>6616565</v>
+        <v>6616548</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,10 +19463,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733712</v>
+        <v>121733585</v>
       </c>
       <c r="B172" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19466,52 +19475,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685256</v>
+        <v>685248</v>
       </c>
       <c r="R172" t="n">
-        <v>6616548</v>
+        <v>6616566</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121744023</v>
+        <v>121542947</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685226</v>
+        <v>685522</v>
       </c>
       <c r="R173" t="n">
-        <v>6616558</v>
+        <v>6616576</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121542947</v>
+        <v>121733047</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19739,21 +19739,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685522</v>
+        <v>685249</v>
       </c>
       <c r="R174" t="n">
-        <v>6616576</v>
+        <v>6616645</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19818,7 +19818,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121733047</v>
+        <v>121744023</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19870,14 +19870,14 @@
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685249</v>
+        <v>685226</v>
       </c>
       <c r="R175" t="n">
-        <v>6616645</v>
+        <v>6616558</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19904,17 +19904,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19942,7 +19942,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121763251</v>
+        <v>121762699</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19996,10 +19996,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685224</v>
+        <v>685226</v>
       </c>
       <c r="R176" t="n">
-        <v>6616549</v>
+        <v>6616562</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20058,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121763551</v>
+        <v>121762474</v>
       </c>
       <c r="B177" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20070,52 +20070,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685221</v>
+        <v>685237</v>
       </c>
       <c r="R177" t="n">
-        <v>6616544</v>
+        <v>6616643</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20148,11 +20134,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20179,10 +20160,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121762474</v>
+        <v>121763251</v>
       </c>
       <c r="B178" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20191,38 +20172,52 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R178" t="n">
-        <v>6616643</v>
+        <v>6616549</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20281,7 +20276,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121762699</v>
+        <v>121763551</v>
       </c>
       <c r="B179" t="n">
         <v>98113</v>
@@ -20316,7 +20311,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -20335,10 +20330,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685226</v>
+        <v>685221</v>
       </c>
       <c r="R179" t="n">
-        <v>6616562</v>
+        <v>6616544</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20371,6 +20366,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -18502,10 +18502,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733409</v>
+        <v>121733533</v>
       </c>
       <c r="B163" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18514,40 +18514,31 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18556,10 +18547,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685237</v>
+        <v>685207</v>
       </c>
       <c r="R163" t="n">
-        <v>6616591</v>
+        <v>6616580</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18618,10 +18609,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733533</v>
+        <v>121733409</v>
       </c>
       <c r="B164" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18630,31 +18621,40 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685207</v>
+        <v>685237</v>
       </c>
       <c r="R164" t="n">
-        <v>6616580</v>
+        <v>6616591</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733778</v>
+        <v>121733238</v>
       </c>
       <c r="B158" t="n">
-        <v>5193</v>
+        <v>94885</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17956,39 +17956,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685216</v>
+        <v>685200</v>
       </c>
       <c r="R158" t="n">
-        <v>6616536</v>
+        <v>6616618</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18047,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733724</v>
+        <v>121733744</v>
       </c>
       <c r="B159" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18059,52 +18054,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685253</v>
+        <v>685241</v>
       </c>
       <c r="R159" t="n">
-        <v>6616553</v>
+        <v>6616545</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18163,10 +18144,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733202</v>
+        <v>121733778</v>
       </c>
       <c r="B160" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18175,20 +18156,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18199,19 +18180,19 @@
       <c r="I160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685225</v>
+        <v>685216</v>
       </c>
       <c r="R160" t="n">
-        <v>6616633</v>
+        <v>6616536</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18386,10 +18367,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733612</v>
+        <v>121733202</v>
       </c>
       <c r="B162" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18398,40 +18379,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18440,10 +18412,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685252</v>
+        <v>685225</v>
       </c>
       <c r="R162" t="n">
-        <v>6616565</v>
+        <v>6616633</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18502,7 +18474,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733533</v>
+        <v>121733466</v>
       </c>
       <c r="B163" t="n">
         <v>57373</v>
@@ -18547,10 +18519,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685207</v>
+        <v>685224</v>
       </c>
       <c r="R163" t="n">
-        <v>6616580</v>
+        <v>6616585</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18609,10 +18581,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733409</v>
+        <v>121733533</v>
       </c>
       <c r="B164" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18621,40 +18593,31 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18663,10 +18626,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685237</v>
+        <v>685207</v>
       </c>
       <c r="R164" t="n">
-        <v>6616591</v>
+        <v>6616580</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18725,7 +18688,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733164</v>
+        <v>121733137</v>
       </c>
       <c r="B165" t="n">
         <v>90728</v>
@@ -18765,10 +18728,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685265</v>
+        <v>685270</v>
       </c>
       <c r="R165" t="n">
-        <v>6616630</v>
+        <v>6616635</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18827,10 +18790,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733744</v>
+        <v>121733242</v>
       </c>
       <c r="B166" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18843,34 +18806,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685241</v>
+        <v>685203</v>
       </c>
       <c r="R166" t="n">
-        <v>6616545</v>
+        <v>6616619</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18929,10 +18897,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733137</v>
+        <v>121733409</v>
       </c>
       <c r="B167" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18941,38 +18909,52 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685270</v>
+        <v>685237</v>
       </c>
       <c r="R167" t="n">
-        <v>6616635</v>
+        <v>6616591</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19031,10 +19013,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733466</v>
+        <v>121733612</v>
       </c>
       <c r="B168" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19043,31 +19025,40 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19076,10 +19067,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685224</v>
+        <v>685252</v>
       </c>
       <c r="R168" t="n">
-        <v>6616585</v>
+        <v>6616565</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19138,10 +19129,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733238</v>
+        <v>121733712</v>
       </c>
       <c r="B169" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19150,38 +19141,52 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685200</v>
+        <v>685256</v>
       </c>
       <c r="R169" t="n">
-        <v>6616618</v>
+        <v>6616548</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19240,10 +19245,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733242</v>
+        <v>121733585</v>
       </c>
       <c r="B170" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19252,31 +19257,31 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19285,10 +19290,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685203</v>
+        <v>685248</v>
       </c>
       <c r="R170" t="n">
-        <v>6616619</v>
+        <v>6616566</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19347,10 +19352,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733712</v>
+        <v>121733164</v>
       </c>
       <c r="B171" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19359,52 +19364,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685256</v>
+        <v>685265</v>
       </c>
       <c r="R171" t="n">
-        <v>6616548</v>
+        <v>6616630</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19463,10 +19454,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733585</v>
+        <v>121733724</v>
       </c>
       <c r="B172" t="n">
-        <v>8436</v>
+        <v>98113</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19475,43 +19466,52 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685248</v>
+        <v>685253</v>
       </c>
       <c r="R172" t="n">
-        <v>6616566</v>
+        <v>6616553</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121542947</v>
+        <v>121733047</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685522</v>
+        <v>685249</v>
       </c>
       <c r="R173" t="n">
-        <v>6616576</v>
+        <v>6616645</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121733047</v>
+        <v>121542947</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19739,21 +19739,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685249</v>
+        <v>685522</v>
       </c>
       <c r="R174" t="n">
-        <v>6616645</v>
+        <v>6616576</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121762699</v>
+        <v>121762474</v>
       </c>
       <c r="B176" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19954,52 +19954,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R176" t="n">
-        <v>6616562</v>
+        <v>6616643</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20058,10 +20044,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762474</v>
+        <v>121762699</v>
       </c>
       <c r="B177" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20070,38 +20056,52 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685237</v>
+        <v>685226</v>
       </c>
       <c r="R177" t="n">
-        <v>6616643</v>
+        <v>6616562</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733238</v>
+        <v>121733744</v>
       </c>
       <c r="B158" t="n">
-        <v>94885</v>
+        <v>90728</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,38 +17952,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685200</v>
+        <v>685241</v>
       </c>
       <c r="R158" t="n">
-        <v>6616618</v>
+        <v>6616545</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733744</v>
+        <v>121733242</v>
       </c>
       <c r="B159" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18058,34 +18058,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685241</v>
+        <v>685203</v>
       </c>
       <c r="R159" t="n">
-        <v>6616545</v>
+        <v>6616619</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18144,10 +18149,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733778</v>
+        <v>121733724</v>
       </c>
       <c r="B160" t="n">
-        <v>5193</v>
+        <v>98113</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18156,43 +18161,52 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685216</v>
+        <v>685253</v>
       </c>
       <c r="R160" t="n">
-        <v>6616536</v>
+        <v>6616553</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18251,10 +18265,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733603</v>
+        <v>121733238</v>
       </c>
       <c r="B161" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18263,52 +18277,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685252</v>
+        <v>685200</v>
       </c>
       <c r="R161" t="n">
-        <v>6616565</v>
+        <v>6616618</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18367,10 +18367,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733202</v>
+        <v>121733712</v>
       </c>
       <c r="B162" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18379,43 +18379,52 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685225</v>
+        <v>685256</v>
       </c>
       <c r="R162" t="n">
-        <v>6616633</v>
+        <v>6616548</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18474,10 +18483,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733466</v>
+        <v>121733164</v>
       </c>
       <c r="B163" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18490,39 +18499,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685224</v>
+        <v>685265</v>
       </c>
       <c r="R163" t="n">
-        <v>6616585</v>
+        <v>6616630</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18688,10 +18692,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733137</v>
+        <v>121733778</v>
       </c>
       <c r="B165" t="n">
-        <v>90728</v>
+        <v>5193</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18700,38 +18704,43 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685270</v>
+        <v>685216</v>
       </c>
       <c r="R165" t="n">
-        <v>6616635</v>
+        <v>6616536</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18790,10 +18799,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733242</v>
+        <v>121733137</v>
       </c>
       <c r="B166" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18806,39 +18815,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685203</v>
+        <v>685270</v>
       </c>
       <c r="R166" t="n">
-        <v>6616619</v>
+        <v>6616635</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18897,10 +18901,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733409</v>
+        <v>121733585</v>
       </c>
       <c r="B167" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18909,40 +18913,31 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -18951,10 +18946,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685237</v>
+        <v>685248</v>
       </c>
       <c r="R167" t="n">
-        <v>6616591</v>
+        <v>6616566</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19129,7 +19124,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733712</v>
+        <v>121733603</v>
       </c>
       <c r="B169" t="n">
         <v>98113</v>
@@ -19164,7 +19159,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19179,14 +19174,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685256</v>
+        <v>685252</v>
       </c>
       <c r="R169" t="n">
-        <v>6616548</v>
+        <v>6616565</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19245,10 +19240,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733585</v>
+        <v>121733466</v>
       </c>
       <c r="B170" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19257,31 +19252,31 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19290,10 +19285,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685248</v>
+        <v>685224</v>
       </c>
       <c r="R170" t="n">
-        <v>6616566</v>
+        <v>6616585</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19352,10 +19347,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733164</v>
+        <v>121733202</v>
       </c>
       <c r="B171" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19368,34 +19363,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685265</v>
+        <v>685225</v>
       </c>
       <c r="R171" t="n">
-        <v>6616630</v>
+        <v>6616633</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,7 +19454,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733724</v>
+        <v>121733409</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19504,14 +19504,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685253</v>
+        <v>685237</v>
       </c>
       <c r="R172" t="n">
-        <v>6616553</v>
+        <v>6616591</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121733047</v>
+        <v>121744023</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19622,14 +19622,14 @@
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685249</v>
+        <v>685226</v>
       </c>
       <c r="R173" t="n">
-        <v>6616645</v>
+        <v>6616558</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121542947</v>
+        <v>121733047</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19739,21 +19739,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685522</v>
+        <v>685249</v>
       </c>
       <c r="R174" t="n">
-        <v>6616576</v>
+        <v>6616645</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19818,7 +19818,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121744023</v>
+        <v>121542947</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19863,21 +19863,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685226</v>
+        <v>685522</v>
       </c>
       <c r="R175" t="n">
-        <v>6616558</v>
+        <v>6616576</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121762474</v>
+        <v>121762699</v>
       </c>
       <c r="B176" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19954,38 +19954,52 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685237</v>
+        <v>685226</v>
       </c>
       <c r="R176" t="n">
-        <v>6616643</v>
+        <v>6616562</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20044,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762699</v>
+        <v>121762474</v>
       </c>
       <c r="B177" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20056,52 +20070,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R177" t="n">
-        <v>6616562</v>
+        <v>6616643</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20160,7 +20160,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121763251</v>
+        <v>121763551</v>
       </c>
       <c r="B178" t="n">
         <v>98113</v>
@@ -20195,7 +20195,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20214,10 +20214,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685224</v>
+        <v>685221</v>
       </c>
       <c r="R178" t="n">
-        <v>6616549</v>
+        <v>6616544</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20250,6 +20250,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20276,7 +20281,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121763551</v>
+        <v>121763251</v>
       </c>
       <c r="B179" t="n">
         <v>98113</v>
@@ -20311,7 +20316,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -20330,10 +20335,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685221</v>
+        <v>685224</v>
       </c>
       <c r="R179" t="n">
-        <v>6616544</v>
+        <v>6616549</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20366,11 +20371,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,7 +17940,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733744</v>
+        <v>121733137</v>
       </c>
       <c r="B158" t="n">
         <v>90728</v>
@@ -17976,14 +17976,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685241</v>
+        <v>685270</v>
       </c>
       <c r="R158" t="n">
-        <v>6616545</v>
+        <v>6616635</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733242</v>
+        <v>121733744</v>
       </c>
       <c r="B159" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18058,39 +18058,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685203</v>
+        <v>685241</v>
       </c>
       <c r="R159" t="n">
-        <v>6616619</v>
+        <v>6616545</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18149,7 +18144,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733724</v>
+        <v>121733712</v>
       </c>
       <c r="B160" t="n">
         <v>98113</v>
@@ -18184,7 +18179,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18203,10 +18198,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685253</v>
+        <v>685256</v>
       </c>
       <c r="R160" t="n">
-        <v>6616553</v>
+        <v>6616548</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18265,10 +18260,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733238</v>
+        <v>121733778</v>
       </c>
       <c r="B161" t="n">
-        <v>94885</v>
+        <v>5193</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18281,34 +18276,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685200</v>
+        <v>685216</v>
       </c>
       <c r="R161" t="n">
-        <v>6616618</v>
+        <v>6616536</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18367,10 +18367,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733712</v>
+        <v>121733585</v>
       </c>
       <c r="B162" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18379,52 +18379,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685256</v>
+        <v>685248</v>
       </c>
       <c r="R162" t="n">
-        <v>6616548</v>
+        <v>6616566</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18483,10 +18474,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733164</v>
+        <v>121733242</v>
       </c>
       <c r="B163" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18499,34 +18490,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685265</v>
+        <v>685203</v>
       </c>
       <c r="R163" t="n">
-        <v>6616630</v>
+        <v>6616619</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18585,10 +18581,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733533</v>
+        <v>121733409</v>
       </c>
       <c r="B164" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18597,31 +18593,40 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18630,10 +18635,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685207</v>
+        <v>685237</v>
       </c>
       <c r="R164" t="n">
-        <v>6616580</v>
+        <v>6616591</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18692,10 +18697,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733778</v>
+        <v>121733612</v>
       </c>
       <c r="B165" t="n">
-        <v>5193</v>
+        <v>105218</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18708,39 +18713,48 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685216</v>
+        <v>685252</v>
       </c>
       <c r="R165" t="n">
-        <v>6616536</v>
+        <v>6616565</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18799,7 +18813,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733137</v>
+        <v>121733164</v>
       </c>
       <c r="B166" t="n">
         <v>90728</v>
@@ -18839,10 +18853,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685270</v>
+        <v>685265</v>
       </c>
       <c r="R166" t="n">
-        <v>6616635</v>
+        <v>6616630</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18901,10 +18915,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733585</v>
+        <v>121733533</v>
       </c>
       <c r="B167" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18913,31 +18927,31 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -18946,10 +18960,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685248</v>
+        <v>685207</v>
       </c>
       <c r="R167" t="n">
-        <v>6616566</v>
+        <v>6616580</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19008,10 +19022,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733612</v>
+        <v>121733466</v>
       </c>
       <c r="B168" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19020,40 +19034,31 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19062,10 +19067,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685252</v>
+        <v>685224</v>
       </c>
       <c r="R168" t="n">
-        <v>6616565</v>
+        <v>6616585</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19124,7 +19129,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733603</v>
+        <v>121733724</v>
       </c>
       <c r="B169" t="n">
         <v>98113</v>
@@ -19159,7 +19164,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19174,14 +19179,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685252</v>
+        <v>685253</v>
       </c>
       <c r="R169" t="n">
-        <v>6616565</v>
+        <v>6616553</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19240,7 +19245,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733466</v>
+        <v>121733202</v>
       </c>
       <c r="B170" t="n">
         <v>57373</v>
@@ -19285,10 +19290,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685224</v>
+        <v>685225</v>
       </c>
       <c r="R170" t="n">
-        <v>6616585</v>
+        <v>6616633</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19347,10 +19352,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733202</v>
+        <v>121733238</v>
       </c>
       <c r="B171" t="n">
-        <v>57373</v>
+        <v>94885</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19359,43 +19364,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685225</v>
+        <v>685200</v>
       </c>
       <c r="R171" t="n">
-        <v>6616633</v>
+        <v>6616618</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,7 +19454,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733409</v>
+        <v>121733603</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19508,10 +19508,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685237</v>
+        <v>685252</v>
       </c>
       <c r="R172" t="n">
-        <v>6616591</v>
+        <v>6616565</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121744023</v>
+        <v>121733047</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19622,14 +19622,14 @@
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685226</v>
+        <v>685249</v>
       </c>
       <c r="R173" t="n">
-        <v>6616558</v>
+        <v>6616645</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121733047</v>
+        <v>121542947</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19739,21 +19739,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685249</v>
+        <v>685522</v>
       </c>
       <c r="R174" t="n">
-        <v>6616645</v>
+        <v>6616576</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19818,7 +19818,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121542947</v>
+        <v>121744023</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19863,21 +19863,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685522</v>
+        <v>685226</v>
       </c>
       <c r="R175" t="n">
-        <v>6616576</v>
+        <v>6616558</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20058,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762474</v>
+        <v>121763251</v>
       </c>
       <c r="B177" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20070,38 +20070,52 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R177" t="n">
-        <v>6616643</v>
+        <v>6616549</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20160,10 +20174,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121763551</v>
+        <v>121762474</v>
       </c>
       <c r="B178" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20172,52 +20186,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685221</v>
+        <v>685237</v>
       </c>
       <c r="R178" t="n">
-        <v>6616544</v>
+        <v>6616643</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20250,11 +20250,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20281,7 +20276,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121763251</v>
+        <v>121763551</v>
       </c>
       <c r="B179" t="n">
         <v>98113</v>
@@ -20316,7 +20311,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -20335,10 +20330,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685224</v>
+        <v>685221</v>
       </c>
       <c r="R179" t="n">
-        <v>6616549</v>
+        <v>6616544</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20371,6 +20366,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121733047</v>
+        <v>121542947</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685249</v>
+        <v>685522</v>
       </c>
       <c r="R173" t="n">
-        <v>6616645</v>
+        <v>6616576</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121542947</v>
+        <v>121733047</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19739,21 +19739,21 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685522</v>
+        <v>685249</v>
       </c>
       <c r="R174" t="n">
-        <v>6616576</v>
+        <v>6616645</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD174" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733137</v>
+        <v>121733202</v>
       </c>
       <c r="B158" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17956,34 +17956,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685270</v>
+        <v>685225</v>
       </c>
       <c r="R158" t="n">
-        <v>6616635</v>
+        <v>6616633</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18047,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733744</v>
+        <v>121733238</v>
       </c>
       <c r="B159" t="n">
-        <v>90728</v>
+        <v>94885</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18054,38 +18059,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685241</v>
+        <v>685200</v>
       </c>
       <c r="R159" t="n">
-        <v>6616545</v>
+        <v>6616618</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18367,10 +18372,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733585</v>
+        <v>121733603</v>
       </c>
       <c r="B162" t="n">
-        <v>8436</v>
+        <v>98113</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18379,31 +18384,40 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18412,10 +18426,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685248</v>
+        <v>685252</v>
       </c>
       <c r="R162" t="n">
-        <v>6616566</v>
+        <v>6616565</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18474,10 +18488,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733242</v>
+        <v>121733744</v>
       </c>
       <c r="B163" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18490,39 +18504,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685203</v>
+        <v>685241</v>
       </c>
       <c r="R163" t="n">
-        <v>6616619</v>
+        <v>6616545</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18697,10 +18706,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733612</v>
+        <v>121733137</v>
       </c>
       <c r="B165" t="n">
-        <v>105218</v>
+        <v>90728</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18709,52 +18718,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685252</v>
+        <v>685270</v>
       </c>
       <c r="R165" t="n">
-        <v>6616565</v>
+        <v>6616635</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18813,10 +18808,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733164</v>
+        <v>121733533</v>
       </c>
       <c r="B166" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18829,34 +18824,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685265</v>
+        <v>685207</v>
       </c>
       <c r="R166" t="n">
-        <v>6616630</v>
+        <v>6616580</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18915,10 +18915,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733533</v>
+        <v>121733724</v>
       </c>
       <c r="B167" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18927,43 +18927,52 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685207</v>
+        <v>685253</v>
       </c>
       <c r="R167" t="n">
-        <v>6616580</v>
+        <v>6616553</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19022,10 +19031,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733466</v>
+        <v>121733612</v>
       </c>
       <c r="B168" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19034,31 +19043,40 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19067,10 +19085,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685224</v>
+        <v>685252</v>
       </c>
       <c r="R168" t="n">
-        <v>6616585</v>
+        <v>6616565</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19129,10 +19147,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733724</v>
+        <v>121733164</v>
       </c>
       <c r="B169" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19141,52 +19159,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685253</v>
+        <v>685265</v>
       </c>
       <c r="R169" t="n">
-        <v>6616553</v>
+        <v>6616630</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19245,10 +19249,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733202</v>
+        <v>121733585</v>
       </c>
       <c r="B170" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19257,31 +19261,31 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19290,10 +19294,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685225</v>
+        <v>685248</v>
       </c>
       <c r="R170" t="n">
-        <v>6616633</v>
+        <v>6616566</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19352,10 +19356,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733238</v>
+        <v>121733466</v>
       </c>
       <c r="B171" t="n">
-        <v>94885</v>
+        <v>57373</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19364,38 +19368,43 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685200</v>
+        <v>685224</v>
       </c>
       <c r="R171" t="n">
-        <v>6616618</v>
+        <v>6616585</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,10 +19463,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733603</v>
+        <v>121733242</v>
       </c>
       <c r="B172" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19466,40 +19475,31 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19508,10 +19508,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685252</v>
+        <v>685203</v>
       </c>
       <c r="R172" t="n">
-        <v>6616565</v>
+        <v>6616619</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121542947</v>
+        <v>121744023</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685522</v>
+        <v>685226</v>
       </c>
       <c r="R173" t="n">
-        <v>6616576</v>
+        <v>6616558</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19818,7 +19818,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121744023</v>
+        <v>121542947</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19863,21 +19863,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685226</v>
+        <v>685522</v>
       </c>
       <c r="R175" t="n">
-        <v>6616558</v>
+        <v>6616576</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20058,7 +20058,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121763251</v>
+        <v>121763551</v>
       </c>
       <c r="B177" t="n">
         <v>98113</v>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20112,10 +20112,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685224</v>
+        <v>685221</v>
       </c>
       <c r="R177" t="n">
-        <v>6616549</v>
+        <v>6616544</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20148,6 +20148,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20174,10 +20179,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121762474</v>
+        <v>121763251</v>
       </c>
       <c r="B178" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20186,38 +20191,52 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R178" t="n">
-        <v>6616643</v>
+        <v>6616549</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20276,10 +20295,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121763551</v>
+        <v>121762474</v>
       </c>
       <c r="B179" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20288,52 +20307,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685221</v>
+        <v>685237</v>
       </c>
       <c r="R179" t="n">
-        <v>6616544</v>
+        <v>6616643</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20366,11 +20371,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733202</v>
+        <v>121733238</v>
       </c>
       <c r="B158" t="n">
-        <v>57373</v>
+        <v>94885</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,43 +17952,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685225</v>
+        <v>685200</v>
       </c>
       <c r="R158" t="n">
-        <v>6616633</v>
+        <v>6616618</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18047,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733238</v>
+        <v>121733202</v>
       </c>
       <c r="B159" t="n">
-        <v>94885</v>
+        <v>57373</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18059,38 +18054,43 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685200</v>
+        <v>685225</v>
       </c>
       <c r="R159" t="n">
-        <v>6616618</v>
+        <v>6616633</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18808,10 +18808,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733533</v>
+        <v>121733724</v>
       </c>
       <c r="B166" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18820,43 +18820,52 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685207</v>
+        <v>685253</v>
       </c>
       <c r="R166" t="n">
-        <v>6616580</v>
+        <v>6616553</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18915,10 +18924,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733724</v>
+        <v>121733533</v>
       </c>
       <c r="B167" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18927,52 +18936,43 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685253</v>
+        <v>685207</v>
       </c>
       <c r="R167" t="n">
-        <v>6616553</v>
+        <v>6616580</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -16447,7 +16447,7 @@
         <v>120740870</v>
       </c>
       <c r="B145" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>121649980</v>
       </c>
       <c r="B157" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733238</v>
+        <v>121733712</v>
       </c>
       <c r="B158" t="n">
-        <v>94885</v>
+        <v>98131</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,38 +17952,52 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685200</v>
+        <v>685256</v>
       </c>
       <c r="R158" t="n">
-        <v>6616618</v>
+        <v>6616548</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18056,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733202</v>
+        <v>121733238</v>
       </c>
       <c r="B159" t="n">
-        <v>57373</v>
+        <v>94903</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18054,43 +18068,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685225</v>
+        <v>685200</v>
       </c>
       <c r="R159" t="n">
-        <v>6616633</v>
+        <v>6616618</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18149,10 +18158,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733712</v>
+        <v>121733744</v>
       </c>
       <c r="B160" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18161,52 +18170,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685256</v>
+        <v>685241</v>
       </c>
       <c r="R160" t="n">
-        <v>6616548</v>
+        <v>6616545</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18265,10 +18260,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733778</v>
+        <v>121733466</v>
       </c>
       <c r="B161" t="n">
-        <v>5193</v>
+        <v>57381</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18277,20 +18272,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18301,19 +18296,19 @@
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685216</v>
+        <v>685224</v>
       </c>
       <c r="R161" t="n">
-        <v>6616536</v>
+        <v>6616585</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18372,10 +18367,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733603</v>
+        <v>121733533</v>
       </c>
       <c r="B162" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18384,40 +18379,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18426,10 +18412,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685252</v>
+        <v>685207</v>
       </c>
       <c r="R162" t="n">
-        <v>6616565</v>
+        <v>6616580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18488,10 +18474,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733744</v>
+        <v>121733724</v>
       </c>
       <c r="B163" t="n">
-        <v>90728</v>
+        <v>98131</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18500,38 +18486,52 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685241</v>
+        <v>685253</v>
       </c>
       <c r="R163" t="n">
-        <v>6616545</v>
+        <v>6616553</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18590,10 +18590,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733409</v>
+        <v>121733242</v>
       </c>
       <c r="B164" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18602,40 +18602,31 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18644,10 +18635,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685237</v>
+        <v>685203</v>
       </c>
       <c r="R164" t="n">
-        <v>6616591</v>
+        <v>6616619</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18706,10 +18697,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733137</v>
+        <v>121733164</v>
       </c>
       <c r="B165" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18746,10 +18737,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685270</v>
+        <v>685265</v>
       </c>
       <c r="R165" t="n">
-        <v>6616635</v>
+        <v>6616630</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18808,10 +18799,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733724</v>
+        <v>121733603</v>
       </c>
       <c r="B166" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18843,7 +18834,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18858,14 +18849,14 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685253</v>
+        <v>685252</v>
       </c>
       <c r="R166" t="n">
-        <v>6616553</v>
+        <v>6616565</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18924,10 +18915,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733533</v>
+        <v>121733612</v>
       </c>
       <c r="B167" t="n">
-        <v>57373</v>
+        <v>105236</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18936,31 +18927,40 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -18969,10 +18969,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685207</v>
+        <v>685252</v>
       </c>
       <c r="R167" t="n">
-        <v>6616580</v>
+        <v>6616565</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19031,10 +19031,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733612</v>
+        <v>121733778</v>
       </c>
       <c r="B168" t="n">
-        <v>105218</v>
+        <v>5193</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19047,48 +19047,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685252</v>
+        <v>685216</v>
       </c>
       <c r="R168" t="n">
-        <v>6616565</v>
+        <v>6616536</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19147,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733164</v>
+        <v>121733202</v>
       </c>
       <c r="B169" t="n">
-        <v>90728</v>
+        <v>57381</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19163,34 +19154,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685265</v>
+        <v>685225</v>
       </c>
       <c r="R169" t="n">
-        <v>6616630</v>
+        <v>6616633</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19249,10 +19245,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733585</v>
+        <v>121733137</v>
       </c>
       <c r="B170" t="n">
-        <v>8436</v>
+        <v>90742</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19261,43 +19257,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685248</v>
+        <v>685270</v>
       </c>
       <c r="R170" t="n">
-        <v>6616566</v>
+        <v>6616635</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19356,10 +19347,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733466</v>
+        <v>121733585</v>
       </c>
       <c r="B171" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19368,31 +19359,31 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19401,10 +19392,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685224</v>
+        <v>685248</v>
       </c>
       <c r="R171" t="n">
-        <v>6616585</v>
+        <v>6616566</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19463,10 +19454,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733242</v>
+        <v>121733409</v>
       </c>
       <c r="B172" t="n">
-        <v>57373</v>
+        <v>98131</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19475,31 +19466,40 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19508,10 +19508,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685203</v>
+        <v>685237</v>
       </c>
       <c r="R172" t="n">
-        <v>6616619</v>
+        <v>6616591</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19573,7 +19573,7 @@
         <v>121744023</v>
       </c>
       <c r="B173" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>121733047</v>
       </c>
       <c r="B174" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>121542947</v>
       </c>
       <c r="B175" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121762699</v>
+        <v>121762474</v>
       </c>
       <c r="B176" t="n">
-        <v>98113</v>
+        <v>90707</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19954,52 +19954,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R176" t="n">
-        <v>6616562</v>
+        <v>6616643</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20058,10 +20044,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121763551</v>
+        <v>121763251</v>
       </c>
       <c r="B177" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20093,7 +20079,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20112,10 +20098,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685221</v>
+        <v>685224</v>
       </c>
       <c r="R177" t="n">
-        <v>6616544</v>
+        <v>6616549</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20148,11 +20134,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20179,10 +20160,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121763251</v>
+        <v>121762699</v>
       </c>
       <c r="B178" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20214,7 +20195,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20233,10 +20214,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685224</v>
+        <v>685226</v>
       </c>
       <c r="R178" t="n">
-        <v>6616549</v>
+        <v>6616562</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20295,10 +20276,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121762474</v>
+        <v>121763551</v>
       </c>
       <c r="B179" t="n">
-        <v>90693</v>
+        <v>98131</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20307,38 +20288,52 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685237</v>
+        <v>685221</v>
       </c>
       <c r="R179" t="n">
-        <v>6616643</v>
+        <v>6616544</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20371,6 +20366,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20400,7 +20400,7 @@
         <v>121813185</v>
       </c>
       <c r="B180" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733712</v>
+        <v>121733238</v>
       </c>
       <c r="B158" t="n">
-        <v>98131</v>
+        <v>94903</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,52 +17952,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685256</v>
+        <v>685200</v>
       </c>
       <c r="R158" t="n">
-        <v>6616548</v>
+        <v>6616618</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18056,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733238</v>
+        <v>121733744</v>
       </c>
       <c r="B159" t="n">
-        <v>94903</v>
+        <v>90742</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18068,38 +18054,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685200</v>
+        <v>685241</v>
       </c>
       <c r="R159" t="n">
-        <v>6616618</v>
+        <v>6616545</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18158,10 +18144,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733744</v>
+        <v>121733712</v>
       </c>
       <c r="B160" t="n">
-        <v>90742</v>
+        <v>98131</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18170,38 +18156,52 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685241</v>
+        <v>685256</v>
       </c>
       <c r="R160" t="n">
-        <v>6616545</v>
+        <v>6616548</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -16447,7 +16447,7 @@
         <v>120740870</v>
       </c>
       <c r="B145" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>121649980</v>
       </c>
       <c r="B157" t="n">
-        <v>90760</v>
+        <v>90762</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733238</v>
+        <v>121733724</v>
       </c>
       <c r="B158" t="n">
-        <v>94903</v>
+        <v>98133</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,38 +17952,52 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685200</v>
+        <v>685253</v>
       </c>
       <c r="R158" t="n">
-        <v>6616618</v>
+        <v>6616553</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18056,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733744</v>
+        <v>121733603</v>
       </c>
       <c r="B159" t="n">
-        <v>90742</v>
+        <v>98133</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18054,38 +18068,52 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685241</v>
+        <v>685252</v>
       </c>
       <c r="R159" t="n">
-        <v>6616545</v>
+        <v>6616565</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18144,10 +18172,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733712</v>
+        <v>121733744</v>
       </c>
       <c r="B160" t="n">
-        <v>98131</v>
+        <v>90744</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18156,52 +18184,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685256</v>
+        <v>685241</v>
       </c>
       <c r="R160" t="n">
-        <v>6616548</v>
+        <v>6616545</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18260,10 +18274,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733466</v>
+        <v>121733409</v>
       </c>
       <c r="B161" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18272,31 +18286,40 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18305,10 +18328,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685224</v>
+        <v>685237</v>
       </c>
       <c r="R161" t="n">
-        <v>6616585</v>
+        <v>6616591</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18367,10 +18390,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733533</v>
+        <v>121733585</v>
       </c>
       <c r="B162" t="n">
-        <v>57381</v>
+        <v>8436</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18379,31 +18402,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18412,10 +18435,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685207</v>
+        <v>685248</v>
       </c>
       <c r="R162" t="n">
-        <v>6616580</v>
+        <v>6616566</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18474,10 +18497,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733724</v>
+        <v>121733466</v>
       </c>
       <c r="B163" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18486,52 +18509,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685253</v>
+        <v>685224</v>
       </c>
       <c r="R163" t="n">
-        <v>6616553</v>
+        <v>6616585</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18590,10 +18604,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733242</v>
+        <v>121733612</v>
       </c>
       <c r="B164" t="n">
-        <v>57381</v>
+        <v>105238</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18602,31 +18616,40 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18635,10 +18658,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685203</v>
+        <v>685252</v>
       </c>
       <c r="R164" t="n">
-        <v>6616619</v>
+        <v>6616565</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18697,10 +18720,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733164</v>
+        <v>121733238</v>
       </c>
       <c r="B165" t="n">
-        <v>90742</v>
+        <v>94905</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18709,38 +18732,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685265</v>
+        <v>685200</v>
       </c>
       <c r="R165" t="n">
-        <v>6616630</v>
+        <v>6616618</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18799,10 +18822,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733603</v>
+        <v>121733137</v>
       </c>
       <c r="B166" t="n">
-        <v>98131</v>
+        <v>90744</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18811,52 +18834,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685252</v>
+        <v>685270</v>
       </c>
       <c r="R166" t="n">
-        <v>6616565</v>
+        <v>6616635</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18915,10 +18924,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733612</v>
+        <v>121733533</v>
       </c>
       <c r="B167" t="n">
-        <v>105236</v>
+        <v>57381</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18927,40 +18936,31 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -18969,10 +18969,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685252</v>
+        <v>685207</v>
       </c>
       <c r="R167" t="n">
-        <v>6616565</v>
+        <v>6616580</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19031,10 +19031,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733778</v>
+        <v>121733202</v>
       </c>
       <c r="B168" t="n">
-        <v>5193</v>
+        <v>57381</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19043,20 +19043,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -19067,19 +19067,19 @@
       <c r="I168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685216</v>
+        <v>685225</v>
       </c>
       <c r="R168" t="n">
-        <v>6616536</v>
+        <v>6616633</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19138,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733202</v>
+        <v>121733778</v>
       </c>
       <c r="B169" t="n">
-        <v>57381</v>
+        <v>5193</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19150,20 +19150,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19174,19 +19174,19 @@
       <c r="I169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685225</v>
+        <v>685216</v>
       </c>
       <c r="R169" t="n">
-        <v>6616633</v>
+        <v>6616536</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19245,10 +19245,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733137</v>
+        <v>121733164</v>
       </c>
       <c r="B170" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19285,10 +19285,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685270</v>
+        <v>685265</v>
       </c>
       <c r="R170" t="n">
-        <v>6616635</v>
+        <v>6616630</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19347,10 +19347,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733585</v>
+        <v>121733712</v>
       </c>
       <c r="B171" t="n">
-        <v>8436</v>
+        <v>98133</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19359,43 +19359,52 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685248</v>
+        <v>685256</v>
       </c>
       <c r="R171" t="n">
-        <v>6616566</v>
+        <v>6616548</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,10 +19463,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733409</v>
+        <v>121733242</v>
       </c>
       <c r="B172" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19466,40 +19475,31 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19508,10 +19508,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685237</v>
+        <v>685203</v>
       </c>
       <c r="R172" t="n">
-        <v>6616591</v>
+        <v>6616619</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,10 +19570,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121744023</v>
+        <v>121733047</v>
       </c>
       <c r="B173" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19622,14 +19622,14 @@
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685226</v>
+        <v>685249</v>
       </c>
       <c r="R173" t="n">
-        <v>6616558</v>
+        <v>6616645</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,10 +19694,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121733047</v>
+        <v>121744023</v>
       </c>
       <c r="B174" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19746,14 +19746,14 @@
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685249</v>
+        <v>685226</v>
       </c>
       <c r="R174" t="n">
-        <v>6616645</v>
+        <v>6616558</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19821,7 +19821,7 @@
         <v>121542947</v>
       </c>
       <c r="B175" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121762474</v>
+        <v>121763251</v>
       </c>
       <c r="B176" t="n">
-        <v>90707</v>
+        <v>98133</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19954,38 +19954,52 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R176" t="n">
-        <v>6616643</v>
+        <v>6616549</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20044,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121763251</v>
+        <v>121762699</v>
       </c>
       <c r="B177" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20079,7 +20093,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20098,10 +20112,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685224</v>
+        <v>685226</v>
       </c>
       <c r="R177" t="n">
-        <v>6616549</v>
+        <v>6616562</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20160,10 +20174,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121762699</v>
+        <v>121762474</v>
       </c>
       <c r="B178" t="n">
-        <v>98131</v>
+        <v>90709</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20172,52 +20186,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R178" t="n">
-        <v>6616562</v>
+        <v>6616643</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20279,7 +20279,7 @@
         <v>121763551</v>
       </c>
       <c r="B179" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>121813185</v>
       </c>
       <c r="B180" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -16447,7 +16447,7 @@
         <v>120740870</v>
       </c>
       <c r="B145" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>121649980</v>
       </c>
       <c r="B157" t="n">
-        <v>90762</v>
+        <v>90763</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733724</v>
+        <v>121733238</v>
       </c>
       <c r="B158" t="n">
-        <v>98133</v>
+        <v>94912</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,52 +17952,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685253</v>
+        <v>685200</v>
       </c>
       <c r="R158" t="n">
-        <v>6616553</v>
+        <v>6616618</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18056,10 +18042,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733603</v>
+        <v>121733409</v>
       </c>
       <c r="B159" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18091,7 +18077,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18110,10 +18096,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685252</v>
+        <v>685237</v>
       </c>
       <c r="R159" t="n">
-        <v>6616565</v>
+        <v>6616591</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18172,10 +18158,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733744</v>
+        <v>121733164</v>
       </c>
       <c r="B160" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18208,14 +18194,14 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685241</v>
+        <v>685265</v>
       </c>
       <c r="R160" t="n">
-        <v>6616545</v>
+        <v>6616630</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18274,10 +18260,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733409</v>
+        <v>121733612</v>
       </c>
       <c r="B161" t="n">
-        <v>98133</v>
+        <v>105245</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18286,40 +18272,40 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18328,10 +18314,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685237</v>
+        <v>685252</v>
       </c>
       <c r="R161" t="n">
-        <v>6616591</v>
+        <v>6616565</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18390,10 +18376,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733585</v>
+        <v>121733744</v>
       </c>
       <c r="B162" t="n">
-        <v>8436</v>
+        <v>90745</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18402,43 +18388,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685248</v>
+        <v>685241</v>
       </c>
       <c r="R162" t="n">
-        <v>6616566</v>
+        <v>6616545</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18497,7 +18478,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733466</v>
+        <v>121733533</v>
       </c>
       <c r="B163" t="n">
         <v>57381</v>
@@ -18542,10 +18523,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685224</v>
+        <v>685207</v>
       </c>
       <c r="R163" t="n">
-        <v>6616585</v>
+        <v>6616580</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18604,10 +18585,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733612</v>
+        <v>121733724</v>
       </c>
       <c r="B164" t="n">
-        <v>105238</v>
+        <v>98140</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18616,52 +18597,52 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685252</v>
+        <v>685253</v>
       </c>
       <c r="R164" t="n">
-        <v>6616565</v>
+        <v>6616553</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18720,10 +18701,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733238</v>
+        <v>121733242</v>
       </c>
       <c r="B165" t="n">
-        <v>94905</v>
+        <v>57381</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18732,38 +18713,43 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685200</v>
+        <v>685203</v>
       </c>
       <c r="R165" t="n">
-        <v>6616618</v>
+        <v>6616619</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18822,10 +18808,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733137</v>
+        <v>121733603</v>
       </c>
       <c r="B166" t="n">
-        <v>90744</v>
+        <v>98140</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18834,38 +18820,52 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685270</v>
+        <v>685252</v>
       </c>
       <c r="R166" t="n">
-        <v>6616635</v>
+        <v>6616565</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18924,10 +18924,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733533</v>
+        <v>121733778</v>
       </c>
       <c r="B167" t="n">
-        <v>57381</v>
+        <v>5193</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18936,20 +18936,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -18960,19 +18960,19 @@
       <c r="I167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685207</v>
+        <v>685216</v>
       </c>
       <c r="R167" t="n">
-        <v>6616580</v>
+        <v>6616536</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19031,7 +19031,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733202</v>
+        <v>121733466</v>
       </c>
       <c r="B168" t="n">
         <v>57381</v>
@@ -19076,10 +19076,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685225</v>
+        <v>685224</v>
       </c>
       <c r="R168" t="n">
-        <v>6616633</v>
+        <v>6616585</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19138,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733778</v>
+        <v>121733585</v>
       </c>
       <c r="B169" t="n">
-        <v>5193</v>
+        <v>8436</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19154,21 +19154,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19179,14 +19179,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685216</v>
+        <v>685248</v>
       </c>
       <c r="R169" t="n">
-        <v>6616536</v>
+        <v>6616566</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19245,10 +19245,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733164</v>
+        <v>121733202</v>
       </c>
       <c r="B170" t="n">
-        <v>90744</v>
+        <v>57381</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19261,34 +19261,39 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685265</v>
+        <v>685225</v>
       </c>
       <c r="R170" t="n">
-        <v>6616630</v>
+        <v>6616633</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19350,7 +19355,7 @@
         <v>121733712</v>
       </c>
       <c r="B171" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19463,10 +19468,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733242</v>
+        <v>121733137</v>
       </c>
       <c r="B172" t="n">
-        <v>57381</v>
+        <v>90745</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19479,39 +19484,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685203</v>
+        <v>685270</v>
       </c>
       <c r="R172" t="n">
-        <v>6616619</v>
+        <v>6616635</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,10 +19570,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121733047</v>
+        <v>121542947</v>
       </c>
       <c r="B173" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685249</v>
+        <v>685522</v>
       </c>
       <c r="R173" t="n">
-        <v>6616645</v>
+        <v>6616576</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,10 +19694,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121744023</v>
+        <v>121733047</v>
       </c>
       <c r="B174" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19746,14 +19746,14 @@
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685226</v>
+        <v>685249</v>
       </c>
       <c r="R174" t="n">
-        <v>6616558</v>
+        <v>6616645</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19818,10 +19818,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121542947</v>
+        <v>121744023</v>
       </c>
       <c r="B175" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19863,21 +19863,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685522</v>
+        <v>685226</v>
       </c>
       <c r="R175" t="n">
-        <v>6616576</v>
+        <v>6616558</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121763251</v>
+        <v>121762699</v>
       </c>
       <c r="B176" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19996,10 +19996,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685224</v>
+        <v>685226</v>
       </c>
       <c r="R176" t="n">
-        <v>6616549</v>
+        <v>6616562</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20058,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762699</v>
+        <v>121762474</v>
       </c>
       <c r="B177" t="n">
-        <v>98133</v>
+        <v>90710</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20070,52 +20070,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R177" t="n">
-        <v>6616562</v>
+        <v>6616643</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20174,10 +20160,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121762474</v>
+        <v>121763251</v>
       </c>
       <c r="B178" t="n">
-        <v>90709</v>
+        <v>98140</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20186,38 +20172,52 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685237</v>
+        <v>685224</v>
       </c>
       <c r="R178" t="n">
-        <v>6616643</v>
+        <v>6616549</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20279,7 +20279,7 @@
         <v>121763551</v>
       </c>
       <c r="B179" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>121813185</v>
       </c>
       <c r="B180" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -19031,10 +19031,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121733466</v>
+        <v>121733585</v>
       </c>
       <c r="B168" t="n">
-        <v>57381</v>
+        <v>8436</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19043,31 +19043,31 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19076,10 +19076,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685224</v>
+        <v>685248</v>
       </c>
       <c r="R168" t="n">
-        <v>6616585</v>
+        <v>6616566</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19138,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733585</v>
+        <v>121733466</v>
       </c>
       <c r="B169" t="n">
-        <v>8436</v>
+        <v>57381</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19150,31 +19150,31 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -19183,10 +19183,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685248</v>
+        <v>685224</v>
       </c>
       <c r="R169" t="n">
-        <v>6616566</v>
+        <v>6616585</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -19352,10 +19352,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733712</v>
+        <v>121733137</v>
       </c>
       <c r="B171" t="n">
-        <v>98140</v>
+        <v>90745</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19364,52 +19364,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685256</v>
+        <v>685270</v>
       </c>
       <c r="R171" t="n">
-        <v>6616548</v>
+        <v>6616635</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19468,10 +19454,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733137</v>
+        <v>121733712</v>
       </c>
       <c r="B172" t="n">
-        <v>90745</v>
+        <v>98140</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19480,38 +19466,52 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685270</v>
+        <v>685256</v>
       </c>
       <c r="R172" t="n">
-        <v>6616635</v>
+        <v>6616548</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY180"/>
+  <dimension ref="A1:AY182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16447,7 +16447,7 @@
         <v>120740870</v>
       </c>
       <c r="B145" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121733238</v>
+        <v>121733712</v>
       </c>
       <c r="B158" t="n">
-        <v>94912</v>
+        <v>98149</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17952,38 +17952,52 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685200</v>
+        <v>685256</v>
       </c>
       <c r="R158" t="n">
-        <v>6616618</v>
+        <v>6616548</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18042,10 +18056,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121733409</v>
+        <v>121733137</v>
       </c>
       <c r="B159" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18054,52 +18068,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685237</v>
+        <v>685270</v>
       </c>
       <c r="R159" t="n">
-        <v>6616591</v>
+        <v>6616635</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18158,10 +18158,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121733164</v>
+        <v>121733242</v>
       </c>
       <c r="B160" t="n">
-        <v>90745</v>
+        <v>57385</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18174,34 +18174,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685265</v>
+        <v>685203</v>
       </c>
       <c r="R160" t="n">
-        <v>6616630</v>
+        <v>6616619</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18260,10 +18265,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121733612</v>
+        <v>121733603</v>
       </c>
       <c r="B161" t="n">
-        <v>105245</v>
+        <v>98149</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18272,40 +18277,40 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18376,10 +18381,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121733744</v>
+        <v>121733238</v>
       </c>
       <c r="B162" t="n">
-        <v>90745</v>
+        <v>94921</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18388,38 +18393,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685241</v>
+        <v>685200</v>
       </c>
       <c r="R162" t="n">
-        <v>6616545</v>
+        <v>6616618</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18478,10 +18483,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121733533</v>
+        <v>121733202</v>
       </c>
       <c r="B163" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18523,10 +18528,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685207</v>
+        <v>685225</v>
       </c>
       <c r="R163" t="n">
-        <v>6616580</v>
+        <v>6616633</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18585,10 +18590,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121733724</v>
+        <v>121733744</v>
       </c>
       <c r="B164" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18597,52 +18602,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685253</v>
+        <v>685241</v>
       </c>
       <c r="R164" t="n">
-        <v>6616553</v>
+        <v>6616545</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18701,10 +18692,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733242</v>
+        <v>121733724</v>
       </c>
       <c r="B165" t="n">
-        <v>57381</v>
+        <v>98149</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18713,43 +18704,52 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685203</v>
+        <v>685253</v>
       </c>
       <c r="R165" t="n">
-        <v>6616619</v>
+        <v>6616553</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18808,10 +18808,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121733603</v>
+        <v>121733778</v>
       </c>
       <c r="B166" t="n">
-        <v>98140</v>
+        <v>5193</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18820,52 +18820,43 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685252</v>
+        <v>685216</v>
       </c>
       <c r="R166" t="n">
-        <v>6616565</v>
+        <v>6616536</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18924,10 +18915,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733778</v>
+        <v>121733612</v>
       </c>
       <c r="B167" t="n">
-        <v>5193</v>
+        <v>105254</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18940,39 +18931,48 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685216</v>
+        <v>685252</v>
       </c>
       <c r="R167" t="n">
-        <v>6616536</v>
+        <v>6616565</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19138,10 +19138,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733466</v>
+        <v>121733164</v>
       </c>
       <c r="B169" t="n">
-        <v>57381</v>
+        <v>90754</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19154,39 +19154,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685224</v>
+        <v>685265</v>
       </c>
       <c r="R169" t="n">
-        <v>6616585</v>
+        <v>6616630</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19245,10 +19240,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733202</v>
+        <v>121733533</v>
       </c>
       <c r="B170" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19290,10 +19285,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685225</v>
+        <v>685207</v>
       </c>
       <c r="R170" t="n">
-        <v>6616633</v>
+        <v>6616580</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19352,10 +19347,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733137</v>
+        <v>121733466</v>
       </c>
       <c r="B171" t="n">
-        <v>90745</v>
+        <v>57385</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19368,34 +19363,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Kalkbarrskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685270</v>
+        <v>685224</v>
       </c>
       <c r="R171" t="n">
-        <v>6616635</v>
+        <v>6616585</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19454,10 +19454,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121733712</v>
+        <v>121733409</v>
       </c>
       <c r="B172" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19504,14 +19504,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685256</v>
+        <v>685237</v>
       </c>
       <c r="R172" t="n">
-        <v>6616548</v>
+        <v>6616591</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19570,10 +19570,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121542947</v>
+        <v>121733047</v>
       </c>
       <c r="B173" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19615,21 +19615,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685522</v>
+        <v>685249</v>
       </c>
       <c r="R173" t="n">
-        <v>6616576</v>
+        <v>6616645</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19656,17 +19656,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
+          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19694,10 +19694,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121733047</v>
+        <v>121744023</v>
       </c>
       <c r="B174" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19746,14 +19746,14 @@
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685249</v>
+        <v>685226</v>
       </c>
       <c r="R174" t="n">
-        <v>6616645</v>
+        <v>6616558</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19780,17 +19780,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Återbesök. 2 en meter norr om de fyra smågranarna, 4 2m norrut vid den gamla tallen</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19818,10 +19818,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121744023</v>
+        <v>121542947</v>
       </c>
       <c r="B175" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19863,21 +19863,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685226</v>
+        <v>685522</v>
       </c>
       <c r="R175" t="n">
-        <v>6616558</v>
+        <v>6616576</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>14 blomstänglar. Ca 1 meter ifrån äldre tall, ca 4 meter nordväst om de två gamla asparna. Inom 1 kvm. Mycket asplöv över det mesta av beståndet.</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19942,10 +19942,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121762699</v>
+        <v>121763251</v>
       </c>
       <c r="B176" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19996,10 +19996,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685226</v>
+        <v>685224</v>
       </c>
       <c r="R176" t="n">
-        <v>6616562</v>
+        <v>6616549</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20058,10 +20058,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121762474</v>
+        <v>121762699</v>
       </c>
       <c r="B177" t="n">
-        <v>90710</v>
+        <v>98149</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20070,38 +20070,52 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685237</v>
+        <v>685226</v>
       </c>
       <c r="R177" t="n">
-        <v>6616643</v>
+        <v>6616562</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20160,10 +20174,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121763251</v>
+        <v>121763551</v>
       </c>
       <c r="B178" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20195,7 +20209,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20214,10 +20228,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685224</v>
+        <v>685221</v>
       </c>
       <c r="R178" t="n">
-        <v>6616549</v>
+        <v>6616544</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20250,6 +20264,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20276,10 +20295,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121763551</v>
+        <v>121762474</v>
       </c>
       <c r="B179" t="n">
-        <v>98140</v>
+        <v>90719</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20288,52 +20307,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685221</v>
+        <v>685237</v>
       </c>
       <c r="R179" t="n">
-        <v>6616544</v>
+        <v>6616643</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20366,11 +20371,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Vid djurstig</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20400,7 +20400,7 @@
         <v>121813185</v>
       </c>
       <c r="B180" t="n">
-        <v>90710</v>
+        <v>90719</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20496,6 +20496,210 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>122104272</v>
+      </c>
+      <c r="B181" t="n">
+        <v>89814</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>889</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Irpicodon pendulus</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>685183</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6616615</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>122129885</v>
+      </c>
+      <c r="B182" t="n">
+        <v>89814</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>889</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Irpicodon pendulus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>685169</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6616602</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY182"/>
+  <dimension ref="A1:AY183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20701,6 +20701,108 @@
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>122391710</v>
+      </c>
+      <c r="B183" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Barrnaturskog sydost om Kårsta, Barrnaturskog sydost om Kårsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>685427</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6616576</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20499,10 +20499,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122104272</v>
+        <v>122129885</v>
       </c>
       <c r="B181" t="n">
-        <v>89839</v>
+        <v>89849</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20535,14 +20535,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685183</v>
+        <v>685169</v>
       </c>
       <c r="R181" t="n">
-        <v>6616615</v>
+        <v>6616602</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20569,12 +20569,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20601,10 +20601,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122129885</v>
+        <v>122104272</v>
       </c>
       <c r="B182" t="n">
-        <v>89839</v>
+        <v>89849</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20637,14 +20637,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685169</v>
+        <v>685183</v>
       </c>
       <c r="R182" t="n">
-        <v>6616602</v>
+        <v>6616615</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20671,12 +20671,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY183"/>
+  <dimension ref="A1:AY182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20499,10 +20499,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122129885</v>
+        <v>122104272</v>
       </c>
       <c r="B181" t="n">
-        <v>89849</v>
+        <v>89861</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20535,14 +20535,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685169</v>
+        <v>685183</v>
       </c>
       <c r="R181" t="n">
-        <v>6616602</v>
+        <v>6616615</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20569,12 +20569,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20601,10 +20601,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122104272</v>
+        <v>122129885</v>
       </c>
       <c r="B182" t="n">
-        <v>89849</v>
+        <v>89861</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20637,14 +20637,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685183</v>
+        <v>685169</v>
       </c>
       <c r="R182" t="n">
-        <v>6616615</v>
+        <v>6616602</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20671,12 +20671,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20700,108 +20700,6 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>122391710</v>
-      </c>
-      <c r="B183" t="n">
-        <v>78646</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Barrnaturskog sydost om Kårsta, Barrnaturskog sydost om Kårsta, Upl</t>
-        </is>
-      </c>
-      <c r="Q183" t="n">
-        <v>685427</v>
-      </c>
-      <c r="R183" t="n">
-        <v>6616576</v>
-      </c>
-      <c r="S183" t="n">
-        <v>10</v>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>Vallentuna</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>Kårsta</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AD183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT183" t="inlineStr"/>
-      <c r="AW183" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX183" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY183" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20499,10 +20499,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122104272</v>
+        <v>122129885</v>
       </c>
       <c r="B181" t="n">
-        <v>89861</v>
+        <v>89865</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20535,14 +20535,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685183</v>
+        <v>685169</v>
       </c>
       <c r="R181" t="n">
-        <v>6616615</v>
+        <v>6616602</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20569,12 +20569,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20601,10 +20601,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122129885</v>
+        <v>122104272</v>
       </c>
       <c r="B182" t="n">
-        <v>89861</v>
+        <v>89865</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20637,14 +20637,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685169</v>
+        <v>685183</v>
       </c>
       <c r="R182" t="n">
-        <v>6616602</v>
+        <v>6616615</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20671,12 +20671,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20499,10 +20499,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122129885</v>
+        <v>122104272</v>
       </c>
       <c r="B181" t="n">
-        <v>89865</v>
+        <v>89870</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20517,11 +20517,6 @@
       <c r="E181" t="n">
         <v>889</v>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Vintertagging</t>
-        </is>
-      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>Irpicodon pendulus</t>
@@ -20535,14 +20530,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685169</v>
+        <v>685183</v>
       </c>
       <c r="R181" t="n">
-        <v>6616602</v>
+        <v>6616615</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20569,12 +20564,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20601,10 +20596,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122104272</v>
+        <v>122129885</v>
       </c>
       <c r="B182" t="n">
-        <v>89865</v>
+        <v>89870</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20619,11 +20614,6 @@
       <c r="E182" t="n">
         <v>889</v>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Vintertagging</t>
-        </is>
-      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>Irpicodon pendulus</t>
@@ -20637,14 +20627,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685183</v>
+        <v>685169</v>
       </c>
       <c r="R182" t="n">
-        <v>6616615</v>
+        <v>6616602</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20671,12 +20661,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20499,10 +20499,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122104272</v>
+        <v>122129885</v>
       </c>
       <c r="B181" t="n">
-        <v>89870</v>
+        <v>89883</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20517,6 +20517,11 @@
       <c r="E181" t="n">
         <v>889</v>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>Irpicodon pendulus</t>
@@ -20530,14 +20535,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685183</v>
+        <v>685169</v>
       </c>
       <c r="R181" t="n">
-        <v>6616615</v>
+        <v>6616602</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20564,12 +20569,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20596,10 +20601,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122129885</v>
+        <v>122104272</v>
       </c>
       <c r="B182" t="n">
-        <v>89870</v>
+        <v>89883</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20614,6 +20619,11 @@
       <c r="E182" t="n">
         <v>889</v>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>Irpicodon pendulus</t>
@@ -20627,14 +20637,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hällmarktallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Hällmarkstallskog sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685169</v>
+        <v>685183</v>
       </c>
       <c r="R182" t="n">
-        <v>6616602</v>
+        <v>6616615</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20661,12 +20671,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20502,7 +20502,7 @@
         <v>122129885</v>
       </c>
       <c r="B181" t="n">
-        <v>89883</v>
+        <v>89896</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>122104272</v>
       </c>
       <c r="B182" t="n">
-        <v>89883</v>
+        <v>89896</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY183"/>
+  <dimension ref="A1:AY184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20832,6 +20832,113 @@
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>123034997</v>
+      </c>
+      <c r="B184" t="n">
+        <v>43822</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>685234</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6616591</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY184"/>
+  <dimension ref="A1:AY187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20939,6 +20939,321 @@
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>123281911</v>
+      </c>
+      <c r="B185" t="n">
+        <v>74802</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>685322</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6616578</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>123281781</v>
+      </c>
+      <c r="B186" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>685325</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6616579</v>
+      </c>
+      <c r="S186" t="n">
+        <v>25</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>123281849</v>
+      </c>
+      <c r="B187" t="n">
+        <v>74855</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>308</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>685323</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6616578</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY187"/>
+  <dimension ref="A1:AY189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281911</v>
+        <v>123281849</v>
       </c>
       <c r="B185" t="n">
-        <v>74802</v>
+        <v>74855</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,25 +20953,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20981,7 +20981,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685322</v>
+        <v>685323</v>
       </c>
       <c r="R185" t="n">
         <v>6616578</v>
@@ -21043,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281781</v>
+        <v>123281911</v>
       </c>
       <c r="B186" t="n">
-        <v>57494</v>
+        <v>74802</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21055,50 +21055,41 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685325</v>
+        <v>685322</v>
       </c>
       <c r="R186" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21154,10 +21145,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281849</v>
+        <v>123281781</v>
       </c>
       <c r="B187" t="n">
-        <v>74855</v>
+        <v>57494</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21170,37 +21161,46 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685323</v>
+        <v>685325</v>
       </c>
       <c r="R187" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21253,6 +21253,219 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>123298978</v>
+      </c>
+      <c r="B188" t="n">
+        <v>94982</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>210</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>685329</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6616522</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>123298643</v>
+      </c>
+      <c r="B189" t="n">
+        <v>94778</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>685309</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6616617</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>123034997</v>
       </c>
       <c r="B184" t="n">
-        <v>43822</v>
+        <v>43825</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281849</v>
+        <v>123281911</v>
       </c>
       <c r="B185" t="n">
-        <v>74855</v>
+        <v>74805</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,25 +20953,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20981,7 +20981,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685323</v>
+        <v>685322</v>
       </c>
       <c r="R185" t="n">
         <v>6616578</v>
@@ -21043,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281911</v>
+        <v>123281849</v>
       </c>
       <c r="B186" t="n">
-        <v>74802</v>
+        <v>74858</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21055,25 +21055,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21083,7 +21083,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685322</v>
+        <v>685323</v>
       </c>
       <c r="R186" t="n">
         <v>6616578</v>
@@ -21148,7 +21148,7 @@
         <v>123281781</v>
       </c>
       <c r="B187" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>123298978</v>
       </c>
       <c r="B188" t="n">
-        <v>94982</v>
+        <v>94985</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>123298643</v>
       </c>
       <c r="B189" t="n">
-        <v>94778</v>
+        <v>94781</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281911</v>
+        <v>123281781</v>
       </c>
       <c r="B185" t="n">
-        <v>74805</v>
+        <v>57497</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,41 +20953,50 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685322</v>
+        <v>685325</v>
       </c>
       <c r="R185" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21043,10 +21052,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281849</v>
+        <v>123281911</v>
       </c>
       <c r="B186" t="n">
-        <v>74858</v>
+        <v>74805</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21055,25 +21064,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21083,7 +21092,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685323</v>
+        <v>685322</v>
       </c>
       <c r="R186" t="n">
         <v>6616578</v>
@@ -21145,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281781</v>
+        <v>123281849</v>
       </c>
       <c r="B187" t="n">
-        <v>57497</v>
+        <v>74858</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21161,46 +21170,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685325</v>
+        <v>685323</v>
       </c>
       <c r="R187" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21256,10 +21256,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123298978</v>
+        <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>94985</v>
+        <v>94783</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21272,43 +21272,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>685329</v>
+        <v>685309</v>
       </c>
       <c r="R188" t="n">
-        <v>6616522</v>
+        <v>6616617</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21367,10 +21358,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>123298643</v>
+        <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>94781</v>
+        <v>94987</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21383,34 +21374,43 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2813</v>
+        <v>210</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>685309</v>
+        <v>685329</v>
       </c>
       <c r="R189" t="n">
-        <v>6616617</v>
+        <v>6616522</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20706,7 +20706,7 @@
         <v>122769726</v>
       </c>
       <c r="B183" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>94783</v>
+        <v>94789</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>94987</v>
+        <v>94993</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20837,7 +20837,7 @@
         <v>123034997</v>
       </c>
       <c r="B184" t="n">
-        <v>43825</v>
+        <v>43831</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>123281781</v>
       </c>
       <c r="B185" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21052,10 +21052,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281849</v>
+        <v>123281911</v>
       </c>
       <c r="B186" t="n">
-        <v>74861</v>
+        <v>74814</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21064,25 +21064,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21092,7 +21092,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685323</v>
+        <v>685322</v>
       </c>
       <c r="R186" t="n">
         <v>6616578</v>
@@ -21154,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281911</v>
+        <v>123281849</v>
       </c>
       <c r="B187" t="n">
-        <v>74808</v>
+        <v>74867</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21166,25 +21166,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685322</v>
+        <v>685323</v>
       </c>
       <c r="R187" t="n">
         <v>6616578</v>
@@ -21256,10 +21256,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123298978</v>
+        <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>94996</v>
+        <v>94809</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21272,43 +21272,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>685329</v>
+        <v>685309</v>
       </c>
       <c r="R188" t="n">
-        <v>6616522</v>
+        <v>6616617</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21367,10 +21358,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>123298643</v>
+        <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>94792</v>
+        <v>95013</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21383,34 +21374,43 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2813</v>
+        <v>210</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>685309</v>
+        <v>685329</v>
       </c>
       <c r="R189" t="n">
-        <v>6616617</v>
+        <v>6616522</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20837,7 +20837,7 @@
         <v>123034997</v>
       </c>
       <c r="B184" t="n">
-        <v>43831</v>
+        <v>43834</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281781</v>
+        <v>123281911</v>
       </c>
       <c r="B185" t="n">
-        <v>57503</v>
+        <v>74817</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,50 +20953,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685325</v>
+        <v>685322</v>
       </c>
       <c r="R185" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21052,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281911</v>
+        <v>123281849</v>
       </c>
       <c r="B186" t="n">
-        <v>74814</v>
+        <v>74870</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21064,25 +21055,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21092,7 +21083,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685322</v>
+        <v>685323</v>
       </c>
       <c r="R186" t="n">
         <v>6616578</v>
@@ -21154,10 +21145,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281849</v>
+        <v>123281781</v>
       </c>
       <c r="B187" t="n">
-        <v>74867</v>
+        <v>57506</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21170,37 +21161,46 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685323</v>
+        <v>685325</v>
       </c>
       <c r="R187" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>94809</v>
+        <v>94815</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20944,7 +20944,7 @@
         <v>123281911</v>
       </c>
       <c r="B185" t="n">
-        <v>74817</v>
+        <v>74818</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21043,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281849</v>
+        <v>123281781</v>
       </c>
       <c r="B186" t="n">
-        <v>74870</v>
+        <v>57507</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21059,37 +21059,46 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685323</v>
+        <v>685325</v>
       </c>
       <c r="R186" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21145,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281781</v>
+        <v>123281849</v>
       </c>
       <c r="B187" t="n">
-        <v>57506</v>
+        <v>74871</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21161,46 +21170,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685325</v>
+        <v>685323</v>
       </c>
       <c r="R187" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>94815</v>
+        <v>94817</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281911</v>
+        <v>123281781</v>
       </c>
       <c r="B185" t="n">
-        <v>74818</v>
+        <v>57507</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,41 +20953,50 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685322</v>
+        <v>685325</v>
       </c>
       <c r="R185" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21043,10 +21052,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281781</v>
+        <v>123281849</v>
       </c>
       <c r="B186" t="n">
-        <v>57507</v>
+        <v>74871</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21059,46 +21068,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685325</v>
+        <v>685323</v>
       </c>
       <c r="R186" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21154,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281849</v>
+        <v>123281911</v>
       </c>
       <c r="B187" t="n">
-        <v>74871</v>
+        <v>74818</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21166,25 +21166,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685323</v>
+        <v>685322</v>
       </c>
       <c r="R187" t="n">
         <v>6616578</v>
@@ -21256,10 +21256,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123298643</v>
+        <v>123298978</v>
       </c>
       <c r="B188" t="n">
-        <v>94817</v>
+        <v>95529</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21272,34 +21272,43 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2813</v>
+        <v>210</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>685309</v>
+        <v>685329</v>
       </c>
       <c r="R188" t="n">
-        <v>6616617</v>
+        <v>6616522</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21358,10 +21367,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>123298978</v>
+        <v>123298643</v>
       </c>
       <c r="B189" t="n">
-        <v>95021</v>
+        <v>95325</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21374,43 +21383,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>685329</v>
+        <v>685309</v>
       </c>
       <c r="R189" t="n">
-        <v>6616522</v>
+        <v>6616617</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AY190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21467,6 +21467,117 @@
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>123945575</v>
+      </c>
+      <c r="B190" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>685242</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6616614</v>
+      </c>
+      <c r="S190" t="n">
+        <v>25</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281781</v>
+        <v>123281911</v>
       </c>
       <c r="B185" t="n">
-        <v>57507</v>
+        <v>74818</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,50 +20953,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685325</v>
+        <v>685322</v>
       </c>
       <c r="R185" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21052,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281849</v>
+        <v>123281781</v>
       </c>
       <c r="B186" t="n">
-        <v>74871</v>
+        <v>57507</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21068,37 +21059,46 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685323</v>
+        <v>685325</v>
       </c>
       <c r="R186" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21154,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281911</v>
+        <v>123281849</v>
       </c>
       <c r="B187" t="n">
-        <v>74818</v>
+        <v>74871</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21166,25 +21166,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685322</v>
+        <v>685323</v>
       </c>
       <c r="R187" t="n">
         <v>6616578</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281911</v>
+        <v>123281781</v>
       </c>
       <c r="B185" t="n">
-        <v>74818</v>
+        <v>57507</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20953,41 +20953,50 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685322</v>
+        <v>685325</v>
       </c>
       <c r="R185" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21043,10 +21052,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281781</v>
+        <v>123281849</v>
       </c>
       <c r="B186" t="n">
-        <v>57507</v>
+        <v>74871</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21059,46 +21068,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685325</v>
+        <v>685323</v>
       </c>
       <c r="R186" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21154,10 +21154,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123281849</v>
+        <v>123281911</v>
       </c>
       <c r="B187" t="n">
-        <v>74871</v>
+        <v>74818</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21166,25 +21166,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685323</v>
+        <v>685322</v>
       </c>
       <c r="R187" t="n">
         <v>6616578</v>
@@ -21256,10 +21256,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123298978</v>
+        <v>123298643</v>
       </c>
       <c r="B188" t="n">
-        <v>95529</v>
+        <v>95325</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21272,43 +21272,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>685329</v>
+        <v>685309</v>
       </c>
       <c r="R188" t="n">
-        <v>6616522</v>
+        <v>6616617</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21367,10 +21358,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>123298643</v>
+        <v>123298978</v>
       </c>
       <c r="B189" t="n">
-        <v>95325</v>
+        <v>95529</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21383,34 +21374,43 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2813</v>
+        <v>210</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>685309</v>
+        <v>685329</v>
       </c>
       <c r="R189" t="n">
-        <v>6616617</v>
+        <v>6616522</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -20941,10 +20941,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>123281781</v>
+        <v>123281849</v>
       </c>
       <c r="B185" t="n">
-        <v>57507</v>
+        <v>74871</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20957,46 +20957,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685325</v>
+        <v>685323</v>
       </c>
       <c r="R185" t="n">
-        <v>6616579</v>
+        <v>6616578</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21052,10 +21043,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123281849</v>
+        <v>123281781</v>
       </c>
       <c r="B186" t="n">
-        <v>74871</v>
+        <v>57507</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21068,37 +21059,46 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685323</v>
+        <v>685325</v>
       </c>
       <c r="R186" t="n">
-        <v>6616578</v>
+        <v>6616579</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY191"/>
+  <dimension ref="A1:AY192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21685,6 +21685,117 @@
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>124821679</v>
+      </c>
+      <c r="B192" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>685191</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6616525</v>
+      </c>
+      <c r="S192" t="n">
+        <v>15</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21690,7 +21690,7 @@
         <v>124821679</v>
       </c>
       <c r="B192" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21692,11 +21692,6 @@
       <c r="B192" t="n">
         <v>56836</v>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY192"/>
+  <dimension ref="A1:AY194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21791,6 +21791,200 @@
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>127637883</v>
+      </c>
+      <c r="B193" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>685274</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6616562</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>127637994</v>
+      </c>
+      <c r="B194" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>685406</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6616547</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21984,6 +21984,107 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>128093557</v>
+      </c>
+      <c r="B195" t="n">
+        <v>90853</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>685338</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6616513</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90854</v>
+        <v>90855</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90855</v>
+        <v>90856</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21796,7 +21796,7 @@
         <v>127637883</v>
       </c>
       <c r="B193" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>127637994</v>
       </c>
       <c r="B194" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90856</v>
+        <v>90862</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY195"/>
+  <dimension ref="A1:AY197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22086,6 +22086,210 @@
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>128631148</v>
+      </c>
+      <c r="B196" t="n">
+        <v>90949</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Barrskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>685242</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6616519</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog. Sannolikt med tall.</t>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>128631038</v>
+      </c>
+      <c r="B197" t="n">
+        <v>92779</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Barrskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>685601</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6616539</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90949</v>
+        <v>90954</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92779</v>
+        <v>92784</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90954</v>
+        <v>90966</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90960</v>
+        <v>90962</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -21990,7 +21990,7 @@
         <v>128093557</v>
       </c>
       <c r="B195" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90962</v>
+        <v>90963</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90963</v>
+        <v>90990</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90990</v>
+        <v>90995</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>90995</v>
+        <v>91000</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY197"/>
+  <dimension ref="A1:AY199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22290,6 +22290,200 @@
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>128912531</v>
+      </c>
+      <c r="B198" t="n">
+        <v>86850</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Porslinsblå spindling</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Cortinarius cumatilis</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>685398</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6616539</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>128912434</v>
+      </c>
+      <c r="B199" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>685251</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6616517</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>91000</v>
+        <v>91004</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86850</v>
+        <v>86854</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>91004</v>
+        <v>91009</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86854</v>
+        <v>86859</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>91011</v>
+        <v>91016</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86866</v>
+        <v>86869</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>91016</v>
+        <v>91022</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86869</v>
+        <v>86872</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22091,7 +22091,7 @@
         <v>128631148</v>
       </c>
       <c r="B196" t="n">
-        <v>91022</v>
+        <v>91026</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>128631038</v>
       </c>
       <c r="B197" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86872</v>
+        <v>86876</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86876</v>
+        <v>86883</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86883</v>
+        <v>86885</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86885</v>
+        <v>86886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY199"/>
+  <dimension ref="A1:AY200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86886</v>
+        <v>86889</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91049</v>
+        <v>91052</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22483,6 +22483,103 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>129443348</v>
+      </c>
+      <c r="B200" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Kårstabyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>685458</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6616544</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86889</v>
+        <v>86891</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22295,7 +22295,7 @@
         <v>128912531</v>
       </c>
       <c r="B198" t="n">
-        <v>86891</v>
+        <v>86895</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>128912434</v>
       </c>
       <c r="B199" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY200"/>
+  <dimension ref="A1:AY201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22580,6 +22580,98 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>129704706</v>
+      </c>
+      <c r="B201" t="n">
+        <v>92005</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Kårstabyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>685172</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6616549</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>129704706</v>
       </c>
       <c r="B201" t="n">
-        <v>92005</v>
+        <v>92006</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>129704706</v>
       </c>
       <c r="B201" t="n">
-        <v>92006</v>
+        <v>92011</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>129704706</v>
       </c>
       <c r="B201" t="n">
-        <v>92011</v>
+        <v>92015</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22489,7 +22489,7 @@
         <v>129443348</v>
       </c>
       <c r="B200" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>129704706</v>
       </c>
       <c r="B201" t="n">
-        <v>92015</v>
+        <v>92017</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22586,7 +22586,7 @@
         <v>129704706</v>
       </c>
       <c r="B201" t="n">
-        <v>92017</v>
+        <v>92020</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22595,6 +22595,11 @@
       </c>
       <c r="E201" t="n">
         <v>6040162</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY201"/>
+  <dimension ref="A1:AY202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22678,6 +22678,113 @@
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>130312769</v>
+      </c>
+      <c r="B202" t="n">
+        <v>75158</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Gransumpskog 800m SO Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>685367</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6616588</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75158</v>
+        <v>75161</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75161</v>
+        <v>75187</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75187</v>
+        <v>75189</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75189</v>
+        <v>75197</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75197</v>
+        <v>75198</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22683,7 +22683,7 @@
         <v>130312769</v>
       </c>
       <c r="B202" t="n">
-        <v>75198</v>
+        <v>75199</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY202"/>
+  <dimension ref="A1:AY203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22785,6 +22785,111 @@
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>132732755</v>
+      </c>
+      <c r="B203" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>685302</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6616588</v>
+      </c>
+      <c r="S203" t="n">
+        <v>20</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50183-2023 artfynd.xlsx
+++ b/artfynd/A 50183-2023 artfynd.xlsx
@@ -22790,7 +22790,7 @@
         <v>132732755</v>
       </c>
       <c r="B203" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
